--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A22306E-5E8D-4AB5-BCB1-742DD4D04404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4978AFB8-F220-4D81-8AF1-7ECB45991E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
-    <sheet name="ProductDataTable" sheetId="3" r:id="rId2"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId3"/>
-    <sheet name="NPCDataTable" sheetId="5" r:id="rId4"/>
+    <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
+    <sheet name="ProductDataTable" sheetId="3" r:id="rId3"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId4"/>
+    <sheet name="RobotDataTable" sheetId="5" r:id="rId5"/>
+    <sheet name="UpgradeDataTable" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +37,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="110">
   <si>
     <t>ItemID</t>
   </si>
@@ -50,9 +74,6 @@
     <t>GrowthTime</t>
   </si>
   <si>
-    <t>MaximumYield</t>
-  </si>
-  <si>
     <t>WaterConsumption</t>
   </si>
   <si>
@@ -112,10 +133,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>BasicCost</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>EventID</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -285,10 +302,6 @@
   <si>
     <t>무슨 일인지 수요가 폭락하였습니다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>NPC</t>
-    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>PurchaseCost</t>
@@ -299,10 +312,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>UpgradeLevel</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>UpgradeCost</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -311,24 +320,176 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>Prototype</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Inventory</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>SubInventory</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>Speed</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Efficiency</t>
     <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prototype</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alpha</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgradeID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuildingKit</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Barn</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainInv</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubInv</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>UpgPerk</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainInvLv1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubInvLv1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeedLv1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EfficLv1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainInvLv2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubInvLv2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpeedLv2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EfficLv2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CornSeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PotatoSeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>CarrotSeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnionSeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StrawberrySeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BlueBerrySeed</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinYield</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxYield</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicPrice</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BasicPrice</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Column</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 일련번호</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 이름</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 기준 가격, 원가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>한 슬롯에 쌓을 수 있는 최대 아이템 수량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 보관 기간(일 단위, -1은 영구 보관)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 분류 타입(Seed, Product, Kit 등)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -934,7 +1095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -946,6 +1107,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -992,7 +1159,14 @@
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1025,6 +1199,48 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1358,13 +1574,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.875" style="2" bestFit="1" customWidth="1"/>
@@ -1372,7 +1587,7 @@
     <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1380,265 +1595,637 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2">
+        <f>D3*80/100</f>
+        <v>800</v>
+      </c>
+      <c r="E2" s="2">
         <v>200</v>
       </c>
-      <c r="E2" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="2">
         <v>50</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1021</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
+        <f>D5*80/100</f>
+        <v>720</v>
+      </c>
+      <c r="E4" s="2">
         <v>200</v>
       </c>
-      <c r="E4" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1022</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
+        <v>900</v>
+      </c>
+      <c r="E5" s="2">
         <v>50</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2011</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
+        <f>D7*80/100</f>
+        <v>800</v>
+      </c>
+      <c r="E6" s="2">
         <v>200</v>
       </c>
-      <c r="E6" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2012</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="2">
         <v>50</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2021</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2">
+        <f>D9*80/100</f>
+        <v>880</v>
+      </c>
+      <c r="E8" s="2">
         <v>200</v>
       </c>
-      <c r="E8" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2022</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E9" s="2">
         <v>50</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>3011</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>93</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
+        <f>D11*80/100</f>
+        <v>960</v>
+      </c>
+      <c r="E10" s="2">
         <v>200</v>
       </c>
-      <c r="E10" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>3012</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1200</v>
+      </c>
+      <c r="E11" s="2">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2">
         <v>15</v>
       </c>
-      <c r="D11" s="2">
-        <v>50</v>
-      </c>
-      <c r="E11" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>3021</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2">
+        <f>D13*80/100</f>
+        <v>880</v>
+      </c>
+      <c r="E12" s="2">
         <v>200</v>
       </c>
-      <c r="E12" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>3022</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E13" s="2">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2">
         <v>15</v>
       </c>
-      <c r="D13" s="2">
-        <v>50</v>
-      </c>
-      <c r="E13" s="2">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2">
+        <f>D15*80/100</f>
+        <v>1600</v>
+      </c>
+      <c r="E14" s="2">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>4012</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="2">
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="2">
+      <c r="F15" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>4013</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="2">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>8011</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
         <v>-1</v>
       </c>
     </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>8012</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>8021</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>8022</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>8031</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>8032</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>8041</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="2">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>8042</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>9011</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I14">
-    <sortCondition ref="A3:A14"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E25">
+    <sortCondition ref="A2:A25"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="A2:A25">
+    <cfRule type="expression" dxfId="11" priority="1">
+      <formula>AND($A2 &gt;= 9000, $A2 &lt; 10000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>AND($A2 &gt;=8000, $A2 &lt; 9000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>AND($A2 &gt;= 4000, $A2 &lt; 5000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="4">
+      <formula>AND($A2 &gt;= 3000, $A2 &lt; 4000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>AND($A2 &gt;= 2000, $A2 &lt; 3000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>AND($A2 &gt;= 1000, $A2 &lt; 2000)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="str" cm="1">
+        <f t="array" ref="A2:A7">TRANSPOSE(ItemDataTable!A1:F1)</f>
+        <v>ItemID</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="str">
+        <v>ItemName</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="str">
+        <v>ItemType</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="str">
+        <v>BasicPrice</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="str">
+        <v>Stack</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="str">
+        <v>StoragePeriod</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
@@ -1647,13 +2234,13 @@
     <col min="4" max="4" width="11.75" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1661,25 +2248,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1012</v>
       </c>
@@ -1695,6 +2285,7 @@
         <v>0.02</v>
       </c>
       <c r="E2" s="2">
+        <f>VLOOKUP(A2, ItemDataTable!A:D,4, FALSE)</f>
         <v>1000</v>
       </c>
       <c r="F2" s="2">
@@ -1704,10 +2295,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1022</v>
       </c>
@@ -1723,6 +2317,7 @@
         <v>0.01</v>
       </c>
       <c r="E3" s="2">
+        <f>VLOOKUP(A3, ItemDataTable!A:D,4, FALSE)</f>
         <v>900</v>
       </c>
       <c r="F3" s="2">
@@ -1732,10 +2327,13 @@
         <v>1</v>
       </c>
       <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2012</v>
       </c>
@@ -1751,6 +2349,7 @@
         <v>0.04</v>
       </c>
       <c r="E4" s="2">
+        <f>VLOOKUP(A4, ItemDataTable!A:D,4, FALSE)</f>
         <v>1000</v>
       </c>
       <c r="F4" s="2">
@@ -1760,10 +2359,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2022</v>
       </c>
@@ -1779,6 +2381,7 @@
         <v>0.05</v>
       </c>
       <c r="E5" s="2">
+        <f>VLOOKUP(A5, ItemDataTable!A:D,4, FALSE)</f>
         <v>1100</v>
       </c>
       <c r="F5" s="2">
@@ -1788,10 +2391,13 @@
         <v>1</v>
       </c>
       <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3012</v>
       </c>
@@ -1807,6 +2413,7 @@
         <v>0.08</v>
       </c>
       <c r="E6" s="2">
+        <f>VLOOKUP(A6, ItemDataTable!A:D,4, FALSE)</f>
         <v>1200</v>
       </c>
       <c r="F6" s="2">
@@ -1816,10 +2423,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>3022</v>
       </c>
@@ -1835,6 +2445,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="E7" s="2">
+        <f>VLOOKUP(A7, ItemDataTable!A:D,4, FALSE)</f>
         <v>1100</v>
       </c>
       <c r="F7" s="2">
@@ -1844,10 +2455,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4012</v>
       </c>
@@ -1863,6 +2477,7 @@
         <v>0.1</v>
       </c>
       <c r="E8" s="2">
+        <f>VLOOKUP(A8, ItemDataTable!A:D,4, FALSE)</f>
         <v>2000</v>
       </c>
       <c r="F8" s="2">
@@ -1872,21 +2487,25 @@
         <v>1</v>
       </c>
       <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>OR($C1="Seed",$C1="Material")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -1900,19 +2519,19 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -1920,7 +2539,7 @@
         <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2">
         <v>0.01</v>
@@ -1929,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1937,7 +2556,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2">
         <v>-0.01</v>
@@ -1946,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1954,7 +2573,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2">
         <v>0.03</v>
@@ -1963,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1971,7 +2590,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2">
         <v>-0.03</v>
@@ -1980,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1988,7 +2607,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6" s="2">
         <v>0.05</v>
@@ -1997,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2005,7 +2624,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2">
         <v>-0.05</v>
@@ -2014,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2022,7 +2641,7 @@
         <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2">
         <v>-0.03</v>
@@ -2031,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2039,7 +2658,7 @@
         <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2">
         <v>0.01</v>
@@ -2048,7 +2667,7 @@
         <v>201</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2056,7 +2675,7 @@
         <v>203</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2">
         <v>0.02</v>
@@ -2065,7 +2684,7 @@
         <v>202</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2073,7 +2692,7 @@
         <v>211</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2">
         <v>0.05</v>
@@ -2082,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2090,7 +2709,7 @@
         <v>212</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2">
         <v>-0.05</v>
@@ -2099,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2107,7 +2726,7 @@
         <v>213</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2">
         <v>0.03</v>
@@ -2116,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2124,7 +2743,7 @@
         <v>214</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2">
         <v>-0.03</v>
@@ -2133,7 +2752,7 @@
         <v>213</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2141,7 +2760,7 @@
         <v>301</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C15" s="2">
         <v>0.03</v>
@@ -2150,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2158,7 +2777,7 @@
         <v>302</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16" s="2">
         <v>-0.03</v>
@@ -2167,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -2175,7 +2794,7 @@
         <v>303</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2">
         <v>0.04</v>
@@ -2184,7 +2803,7 @@
         <v>302</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2192,7 +2811,7 @@
         <v>304</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2">
         <v>-0.02</v>
@@ -2201,7 +2820,7 @@
         <v>302</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2209,7 +2828,7 @@
         <v>311</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2">
         <v>0.04</v>
@@ -2218,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2226,7 +2845,7 @@
         <v>312</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2">
         <v>-0.03</v>
@@ -2235,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2244,28 +2863,31 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A20">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="6.75" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="3"/>
@@ -2273,42 +2895,42 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>72</v>
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2318,226 +2940,180 @@
       <c r="B3" s="3">
         <v>10000</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>72</v>
+      <c r="C3" s="3">
+        <v>20</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
       <c r="E3" s="3">
-        <v>20000</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>72</v>
+        <v>20000</v>
+      </c>
+      <c r="C4" s="3">
+        <v>40</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="3">
-        <v>40000</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>20000</v>
-      </c>
-      <c r="F6" s="3">
         <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3">
-        <v>40000</v>
-      </c>
-      <c r="F7" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2</v>
-      </c>
-      <c r="E9" s="3">
-        <v>20000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3">
-        <v>40000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>20000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="3">
-        <v>3</v>
-      </c>
-      <c r="E13" s="3">
-        <v>40000</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>Prototype</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715291B3-9102-4FF1-A4AF-13D65BEE1B70}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F6">
+    <sortCondition descending="1" ref="B2:B6"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B13">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>Prototype</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4978AFB8-F220-4D81-8AF1-7ECB45991E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C13B32-83A9-4E12-925B-A8E02BF7BB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
     <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
     <sheet name="ProductDataTable" sheetId="3" r:id="rId3"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId4"/>
-    <sheet name="RobotDataTable" sheetId="5" r:id="rId5"/>
-    <sheet name="UpgradeDataTable" sheetId="6" r:id="rId6"/>
+    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId4"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId5"/>
+    <sheet name="RobotDataTable" sheetId="5" r:id="rId6"/>
+    <sheet name="UpgradeDataTable" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="120">
   <si>
     <t>ItemID</t>
   </si>
@@ -157,58 +158,30 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>일시적으로 수요가 증가한 것으로 보입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DemandDecrease</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>일시적으로 수요가 감소한 것으로 보입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DemandSurge</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>수요가 급격히 증가했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DemandCollapse</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>수요가 급격히 감소했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DiseaseOutbreak</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>연구실에서 유해할 수 있는 병원체가 발견되었다는 소식 입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DiseaseUnderControl</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>병원균에 대한 연구가 꾸준히 이루어지고 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DiseaseContained</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>병원균 백신 개발이 성공적으로 이루어졌습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>PoorHarvest</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -245,62 +218,30 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>섭취한 사람들로부터 체질 개선이 되었다는 소식입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>FoodSafetyInvestigation</t>
   </si>
   <si>
-    <t>지난 주에 사망한 A씨의 사인에 연관이 있을 것으로 추측됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ClearedOfSuspiction</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>다행히도 A씨의 사인에 직접적인 영향을 끼치진 않았습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>FestivalSeason</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>축제로 인해 수요가 증가하고 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>HarvestDrive</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>청년들의 지원 사업으로 생산량이 크게 증가했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>CauseUnderInvestigation</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>A씨의 사인에 대한 원인 분석이 지연되고 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>DemandIExplosion</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>DemandCrash</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>폭발적인 반응과 함께 수요도 폭발하고 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>무슨 일인지 수요가 폭락하였습니다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -489,6 +430,106 @@
   </si>
   <si>
     <t>아이템 분류 타입(Seed, Product, Kit 등)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ItemName}의 수요가 일시적으로 증가한 것으로 보입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ItemName}의 수요가 일시적으로 감소한 것으로 보입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ItemName}의 수요가 급격히 증가했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ItemName}의 수요가 급격히 감소했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>폭발적인 반응과 함께 {ItemName}의 수요도 폭발하고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>무슨 일인지 {ItemName}의 수요가 폭락하였습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아가레아산 {ItemName}에서 발견되었다는 병원균에 대한 연구가 꾸준히 이루어지고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>드디어 {ItemName}의 병원균 백신 개발이 성공적으로 이루어졌습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>식품 연구소에서 온 보도인데요, 유해할 수 있는 병원균이 아가레아산 {ItemName}에서 발견되었다는 소식 입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ItemName}을(를) 섭취한 사람들로부터 체질 개선이 되었다는 소식입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지난 주에 사망한 A씨의 사인에 그가 구매했던 {ItemName}이 주된 원인이라는 의혹이 나오고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>A씨의 사인에 대한 원인 분석이 지연되고 있습니다. 그에 따라 {ItemName}의 가격도 지속적으로 하락하고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{ItemName} 축제로 인해 수요가 증가하고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>청년들의 지원 사업으로 {ItemName}의 생산량이 크게 증가했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다행히도 {ItemName}은(는) A씨의 사인에 직접적인 영향을 끼치진 않았습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 분류 타입</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격 변동 표준편차</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>원가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>성장 시간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최대 수확량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최소 수확량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수분 소모량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>enum</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1111,8 +1152,8 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1159,46 +1200,46 @@
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="24">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.39994506668294322"/>
+          <bgColor rgb="FF0070C0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1241,6 +1282,90 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1574,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
@@ -1598,7 +1723,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
@@ -1609,20 +1734,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1011</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="D2" s="2">
-        <f>D3*80/100</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2">
         <v>-1</v>
@@ -1630,302 +1754,303 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2">
-        <v>1000</v>
+        <f>D4*80/100</f>
+        <v>800</v>
       </c>
       <c r="E3" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F3" s="2">
-        <v>30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>9</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
-        <f>D5*80/100</f>
-        <v>720</v>
+        <v>1000</v>
       </c>
       <c r="E4" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
-        <v>900</v>
+        <f>D6*80/100</f>
+        <v>720</v>
       </c>
       <c r="E5" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F5" s="2">
-        <v>30</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>2011</v>
+        <v>1022</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2">
-        <f>D7*80/100</f>
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E6" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>-1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2">
-        <v>1000</v>
+        <f>D8*80/100</f>
+        <v>800</v>
       </c>
       <c r="E7" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F7" s="2">
-        <v>20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
-        <f>D9*80/100</f>
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="E8" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F8" s="2">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2">
-        <v>1100</v>
+        <f>D10*80/100</f>
+        <v>880</v>
       </c>
       <c r="E9" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>3011</v>
+        <v>2022</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2">
-        <f>D11*80/100</f>
-        <v>960</v>
+        <v>1100</v>
       </c>
       <c r="E10" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>-1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
-        <v>1200</v>
+        <f>D12*80/100</f>
+        <v>960</v>
       </c>
       <c r="E11" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F11" s="2">
-        <v>15</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>3021</v>
+        <v>3012</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2">
-        <f>D13*80/100</f>
-        <v>880</v>
+        <v>1200</v>
       </c>
       <c r="E12" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>-1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
-        <v>1100</v>
+        <f>D14*80/100</f>
+        <v>880</v>
       </c>
       <c r="E13" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F13" s="2">
-        <v>15</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>4011</v>
+        <v>3022</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="2">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2">
         <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2">
-        <f>D15*80/100</f>
-        <v>1600</v>
-      </c>
-      <c r="E14" s="2">
-        <v>10</v>
-      </c>
-      <c r="F14" s="2">
-        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2">
-        <v>2000</v>
+        <f>D16*80/100</f>
+        <v>1600</v>
       </c>
       <c r="E15" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F15" s="2">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>8011</v>
+        <v>4012</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
       </c>
       <c r="F16" s="2">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D17" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -1936,16 +2061,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8021</v>
+        <v>8012</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -1956,16 +2081,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8022</v>
+        <v>8021</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D19" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -1976,16 +2101,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8031</v>
+        <v>8022</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -1996,16 +2121,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8032</v>
+        <v>8031</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -2016,16 +2141,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8041</v>
+        <v>8032</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D22" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -2036,16 +2161,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8042</v>
+        <v>8041</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D23" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2056,16 +2181,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>9011</v>
+        <v>8042</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2076,13 +2201,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>9021</v>
+        <v>9011</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D25" s="2">
         <v>50000</v>
@@ -2094,29 +2219,49 @@
         <v>-1</v>
       </c>
     </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E25">
-    <sortCondition ref="A2:A25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F26">
+    <sortCondition ref="A2:A26"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A25">
+  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="11" priority="1">
-      <formula>AND($A2 &gt;= 9000, $A2 &lt; 10000)</formula>
+      <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>AND($A2 &gt;=8000, $A2 &lt; 9000)</formula>
+      <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="9" priority="3">
-      <formula>AND($A2 &gt;= 4000, $A2 &lt; 5000)</formula>
+      <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="4">
-      <formula>AND($A2 &gt;= 3000, $A2 &lt; 4000)</formula>
+      <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="5">
-      <formula>AND($A2 &gt;= 2000, $A2 &lt; 3000)</formula>
+      <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="6">
-      <formula>AND($A2 &gt;= 1000, $A2 &lt; 2000)</formula>
+      <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2140,80 +2285,80 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="str" cm="1">
+      <c r="A2" s="2" t="str" cm="1">
         <f t="array" ref="A2:A7">TRANSPOSE(ItemDataTable!A1:F1)</f>
         <v>ItemID</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>102</v>
+      <c r="B2" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="str">
+      <c r="A3" s="2" t="str">
         <v>ItemName</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="str">
+      <c r="A4" s="2" t="str">
         <v>ItemType</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="str">
+      <c r="A5" s="2" t="str">
         <v>BasicPrice</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="str">
+      <c r="A6" s="2" t="str">
         <v>Stack</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="str">
+      <c r="A7" s="2" t="str">
         <v>StoragePeriod</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2254,16 +2399,16 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -2496,7 +2641,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="23" priority="1">
       <formula>OR($C1="Seed",$C1="Material")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2506,6 +2651,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A10">TRANSPOSE(ProductDataTable!A1:I1)</f>
+        <v>ItemID</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>ItemName</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>ItemType</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>PriceStdDev</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>BasicPrice</v>
+      </c>
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>GrowthTime</v>
+      </c>
+      <c r="B7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>MaxYield</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>MinYield</v>
+      </c>
+      <c r="B9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>WaterConsumption</v>
+      </c>
+      <c r="B10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2513,7 +2785,7 @@
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="2"/>
-    <col min="5" max="5" width="59.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="106.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2548,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2556,7 +2828,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2">
         <v>-0.01</v>
@@ -2565,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2573,7 +2845,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2">
         <v>0.03</v>
@@ -2582,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2590,7 +2862,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2">
         <v>-0.03</v>
@@ -2599,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2607,7 +2879,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C6" s="2">
         <v>0.05</v>
@@ -2616,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2624,7 +2896,7 @@
         <v>106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2">
         <v>-0.05</v>
@@ -2633,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2641,7 +2913,7 @@
         <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2">
         <v>-0.03</v>
@@ -2650,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2658,7 +2930,7 @@
         <v>202</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2">
         <v>0.01</v>
@@ -2667,7 +2939,7 @@
         <v>201</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -2675,7 +2947,7 @@
         <v>203</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2">
         <v>0.02</v>
@@ -2684,7 +2956,7 @@
         <v>202</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -2692,7 +2964,7 @@
         <v>211</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2">
         <v>0.05</v>
@@ -2701,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -2709,7 +2981,7 @@
         <v>212</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2">
         <v>-0.05</v>
@@ -2718,7 +2990,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -2726,7 +2998,7 @@
         <v>213</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2">
         <v>0.03</v>
@@ -2735,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -2743,7 +3015,7 @@
         <v>214</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>-0.03</v>
@@ -2752,7 +3024,7 @@
         <v>213</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -2760,7 +3032,7 @@
         <v>301</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2">
         <v>0.03</v>
@@ -2769,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -2777,7 +3049,7 @@
         <v>302</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2">
         <v>-0.03</v>
@@ -2786,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -2794,7 +3066,7 @@
         <v>303</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2">
         <v>0.04</v>
@@ -2803,7 +3075,7 @@
         <v>302</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -2811,7 +3083,7 @@
         <v>304</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2">
         <v>-0.02</v>
@@ -2820,7 +3092,7 @@
         <v>302</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -2828,7 +3100,7 @@
         <v>311</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2">
         <v>0.04</v>
@@ -2837,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2845,7 +3117,7 @@
         <v>312</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2">
         <v>-0.03</v>
@@ -2854,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2863,13 +3135,13 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A20">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="21" priority="2">
       <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="20" priority="3">
       <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2878,7 +3150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -2895,27 +3167,27 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -2935,7 +3207,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3">
         <v>10000</v>
@@ -2955,7 +3227,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3">
         <v>20000</v>
@@ -2976,7 +3248,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>Prototype</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2985,7 +3257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715291B3-9102-4FF1-A4AF-13D65BEE1B70}">
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3001,22 +3273,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -3109,7 +3381,7 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="B1:B13">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>Prototype</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C13B32-83A9-4E12-925B-A8E02BF7BB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688725DA-CC48-4963-A11D-215BA8DEC5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="742" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="123">
   <si>
     <t>ItemID</t>
   </si>
@@ -530,6 +530,18 @@
   </si>
   <si>
     <t>Water</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseToDemo</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BatteryLv1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battery</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1200,11 +1212,39 @@
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1218,21 +1258,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
+          <bgColor theme="7" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1240,90 +1266,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1699,7 +1641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
@@ -1707,12 +1649,15 @@
     <col min="3" max="4" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="13.875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="13.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.5" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1731,326 +1676,374 @@
       <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>1001</v>
+        <v>1011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <f>D3*80/100</f>
+        <v>800</v>
       </c>
       <c r="E2" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1021</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2">
-        <f>D4*80/100</f>
+      <c r="D4" s="2">
+        <f>D5*80/100</f>
+        <v>720</v>
+      </c>
+      <c r="E4" s="2">
+        <v>200</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1022</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2">
+        <v>900</v>
+      </c>
+      <c r="E5" s="2">
+        <v>50</v>
+      </c>
+      <c r="F5" s="2">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
+        <f>D7*80/100</f>
         <v>800</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E6" s="2">
         <v>200</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F6" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>1012</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D7" s="2">
         <v>1000</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E7" s="2">
         <v>50</v>
       </c>
-      <c r="F4" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>1021</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="F7" s="2">
+        <v>20</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="2">
-        <f>D6*80/100</f>
-        <v>720</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D8" s="2">
+        <f>D9*80/100</f>
+        <v>880</v>
+      </c>
+      <c r="E8" s="2">
         <v>200</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F8" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>1022</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="2">
-        <v>900</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D9" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E9" s="2">
         <v>50</v>
       </c>
-      <c r="F6" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>2011</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="F9" s="2">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>3011</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="2">
-        <f>D8*80/100</f>
-        <v>800</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D10" s="2">
+        <f>D11*80/100</f>
+        <v>960</v>
+      </c>
+      <c r="E10" s="2">
         <v>200</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F10" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>2012</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>3012</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D11" s="2">
+        <v>1200</v>
+      </c>
+      <c r="E11" s="2">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>3021</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2">
+        <f>D13*80/100</f>
+        <v>880</v>
+      </c>
+      <c r="E12" s="2">
+        <v>200</v>
+      </c>
+      <c r="F12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>3022</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1100</v>
+      </c>
+      <c r="E13" s="2">
+        <v>50</v>
+      </c>
+      <c r="F13" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2">
+        <f>D15*80/100</f>
+        <v>1600</v>
+      </c>
+      <c r="E14" s="2">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>7011</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="2">
         <v>1000</v>
-      </c>
-      <c r="E8" s="2">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="2">
-        <f>D10*80/100</f>
-        <v>880</v>
-      </c>
-      <c r="E9" s="2">
-        <v>200</v>
-      </c>
-      <c r="F9" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E10" s="2">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>3011</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="2">
-        <f>D12*80/100</f>
-        <v>960</v>
-      </c>
-      <c r="E11" s="2">
-        <v>200</v>
-      </c>
-      <c r="F11" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>3012</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1200</v>
-      </c>
-      <c r="E12" s="2">
-        <v>50</v>
-      </c>
-      <c r="F12" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>3021</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="2">
-        <f>D14*80/100</f>
-        <v>880</v>
-      </c>
-      <c r="E13" s="2">
-        <v>200</v>
-      </c>
-      <c r="F13" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>3022</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="2">
-        <v>1100</v>
-      </c>
-      <c r="E14" s="2">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>4011</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2">
-        <f>D16*80/100</f>
-        <v>1600</v>
-      </c>
-      <c r="E15" s="2">
-        <v>10</v>
-      </c>
-      <c r="F15" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>4012</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2000</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
-      <c r="F16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>8011</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="2">
-        <v>10000</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -2058,19 +2051,22 @@
       <c r="F17" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D18" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -2078,19 +2074,22 @@
       <c r="F18" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8021</v>
+        <v>8012</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -2098,19 +2097,22 @@
       <c r="F19" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8022</v>
+        <v>8021</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D20" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -2118,19 +2120,22 @@
       <c r="F20" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8031</v>
+        <v>8022</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D21" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -2138,19 +2143,22 @@
       <c r="F21" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8032</v>
+        <v>8031</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D22" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -2158,19 +2166,22 @@
       <c r="F22" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8041</v>
+        <v>8032</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2178,19 +2189,22 @@
       <c r="F23" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8042</v>
+        <v>8041</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D24" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2198,19 +2212,22 @@
       <c r="F24" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>9011</v>
+        <v>8042</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D25" s="2">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2218,13 +2235,16 @@
       <c r="F25" s="2">
         <v>-1</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>9021</v>
+        <v>9011</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>61</v>
@@ -2238,30 +2258,62 @@
       <c r="F26" s="2">
         <v>-1</v>
       </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F26">
-    <sortCondition ref="A2:A26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G27">
+    <sortCondition ref="A2:A27"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2641,7 +2693,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="23" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>OR($C1="Seed",$C1="Material")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3135,13 +3187,13 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A20">
-    <cfRule type="expression" dxfId="22" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3248,7 +3300,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>Prototype</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3381,7 +3433,7 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="B1:B13">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>Prototype</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688725DA-CC48-4963-A11D-215BA8DEC5D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276CF695-9D11-4887-BDD3-E0C8B8D5DBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="742" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="6" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="ProductDataTable" sheetId="3" r:id="rId3"/>
     <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId4"/>
     <sheet name="EventDataTable" sheetId="4" r:id="rId5"/>
-    <sheet name="RobotDataTable" sheetId="5" r:id="rId6"/>
-    <sheet name="UpgradeDataTable" sheetId="6" r:id="rId7"/>
+    <sheet name="ObjectDataTable" sheetId="5" r:id="rId6"/>
+    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId7"/>
+    <sheet name="ConfigurationDataTable" sheetId="9" r:id="rId8"/>
+    <sheet name="ConfigurationDataTable_Meta" sheetId="10" r:id="rId9"/>
+    <sheet name="ScenarioDataTable" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="189">
   <si>
     <t>ItemID</t>
   </si>
@@ -243,36 +246,12 @@
   <si>
     <t>DemandCrash</t>
     <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PurchaseCost</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeType</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeCost</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Value</t>
-    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>Speed</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>Efficiency</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>Model</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>Player</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -281,18 +260,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Alpha</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>UpgradeID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Storage</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -542,6 +509,306 @@
   </si>
   <si>
     <t>Battery</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameDayDuration</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>인게임 하루 주기(분)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TutorialEnabled</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>boolean</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼 On/Off</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cow</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectName</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cattle</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>SynarioID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speaker</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetUI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_StoryTelling_TextBox</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI_Chat_TextBox</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>….{PlayerName}님 괜찮으신가요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>음, 로딩이 아직 덜 됐나.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3, 2, 1, {PlayerName}님. 눈을 떠 보시겠어요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 다행이네요, 무사히 투영된 것 같아서.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오, 성공했다고 보면 되나요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 반쪽짜리 성공이라고 보시면 되겠네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>저희 프로젝트는 이제 시작이라고 봐야 하겠지만, 시작이 반이다 뭐 그런 말이 있잖아요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 그럼 우선 뭐 부터 해야 할까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그 슈트에 대한 조작법부터 간단히 알려드리도록 할게요. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>좋아요. 원하는 위치로 이동하고 싶다면 지금처럼 하시면 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 화면에 밝게 빛나는 타일에 우클릭을 해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음으로 창고 건물에 좌클릭을 해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Category</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial_Basic</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>루크</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘했어요. 건물이나 NPC들에게 좌클릭을 하면 인터페이스가 뜨는 등의 상호작용을 할 수 있어요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>반대로 창고에 아이템을 넣고 싶다면 똑같이 더블 클릭하거나 창고 슬롯으로 드래그 하면 되죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자. 이제 창고에서 볼일은 끝났으니 나가볼까요? 나가는 버튼은 많이 익숙하실 것 같네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>… 천천히 알려드릴테니 재촉하진 말아주세요…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우측 하단에 표시한 버튼을 눌러보시겠어요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>네 잘하셨어요. 그 버튼을 누르시면 건축 모드로 들어가게 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 모드에서는 다른 오브젝트들이 전부 블러 처리가 되어서 건축을 할 때 도움이 되실 겁니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 아래에 밭을 눌러보시면 밭에 대한 정보도 볼 수 있고, 마우스 포인터 위치에 따른 프리뷰도 보실 수 있답니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>원하시는 위치에 밭을 설치해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘하셨어요. 이제 종료 버튼을 누르시면 건축 모드를 종료하실 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고에 있는 씨감자를 더블 클릭하거나 하단 인벤토리 왼쪽 칸에 드래그하면 아이템을 꺼낼 수 있답니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자를 꺼내긴 했는데 잔디밭에 그냥 묻을 수도 없고… 밭을 만들거나 하는 방법은요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>드디어 이 행성에서의 첫 농사를 시작할 수 있겠네요!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠깐, 그런데 밭에 물은 안 줘도 괜찮나요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럴리가요. 지구에서 자랐던 식물인데 물은 당연히 필요하죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 창고 옆에 있는 "하이드로 리엑터"에 우클릭해서 이동해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보조 인벤토리에 물병 아이템이 생긴게 보이죠? 물병을 얻으려면 꼭 하이드로 리엑터에 우클릭을 해야 합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 {2}번 키를 눌러서 물병을 사용할 준비를 해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그 상태로 밭에 상호작용을 하면 물병의 물을 사용해서 밭에 수분을 공급할 수 있답니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수분은 작물이 성장할 때 마다 일정량이 소모되고, 수분이 부족하면 성장이 멈추게 되니 밭의 수분량을 꼭 신경쓰세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 {1번} 키를 눌러서 씨감자 봉지를 사용해볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 밭의 각 칸에 상호작용을 해서 감자를 모두 심어보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘했습니다. 이제 감자가 다 자랄 때 까지 기다리시면 되는데... 기다리기엔 시간이 없으니 이번에는 바로 자란 시점으로 가볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다 자란 감자에도 똑같이 상호작용을 하시면 수확을 하실 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확한 감자는 가운데에 메인 인벤토리에 저장이 됩니다. 이 아이템도 씨앗처럼 창고에 저장할 수 있죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>특히 창고에 저장하지 않고 들고 다니면 작물이 더 빠르게 썩을 수 있으니 되도록 바로 창고에 넣는걸 추천드립니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러면 이걸 팔면 전부 제 돈인거죠? 그런데 이걸 팔려면 본부까지 보내야 할텐데…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>걱정하지 마세요. 창고에 다시 한 번 상호작용 해보시겠어요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chicken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>WorkDuration</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>ProductionAmount</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트 일련번호</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트 이름</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트 분류 타입(PC, NPC 등)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트 구매 가격</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트의 메인 인벤토리 기본 수량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트의 서브 인벤토리 기본 수량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트가 한 칸 이동할 때 걸리는 시간(초)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트가 일을 할 때 걸리는 시간(초)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트가 하루동안 생산할 수 있는 아이템 수량</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>데모버전 사용 여부</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -549,6 +816,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1148,7 +1419,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1165,6 +1436,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,70 +1495,7 @@
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="13">
     <dxf>
       <fill>
         <patternFill>
@@ -1308,6 +1528,62 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1668,7 +1944,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
@@ -1677,7 +1953,7 @@
         <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1685,7 +1961,7 @@
         <v>1011</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>13</v>
@@ -1732,7 +2008,7 @@
         <v>1021</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>13</v>
@@ -1779,7 +2055,7 @@
         <v>2011</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
@@ -1826,7 +2102,7 @@
         <v>2021</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>13</v>
@@ -1873,7 +2149,7 @@
         <v>3011</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
@@ -1920,7 +2196,7 @@
         <v>3021</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>13</v>
@@ -2014,10 +2290,10 @@
         <v>5001</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D16" s="2">
         <v>0</v>
@@ -2037,10 +2313,10 @@
         <v>7011</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D17" s="2">
         <v>1000</v>
@@ -2060,10 +2336,10 @@
         <v>8011</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D18" s="2">
         <v>10000</v>
@@ -2083,10 +2359,10 @@
         <v>8012</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2">
         <v>20000</v>
@@ -2106,10 +2382,10 @@
         <v>8021</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D20" s="2">
         <v>10000</v>
@@ -2129,10 +2405,10 @@
         <v>8022</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2">
         <v>20000</v>
@@ -2152,10 +2428,10 @@
         <v>8031</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D22" s="2">
         <v>10000</v>
@@ -2175,10 +2451,10 @@
         <v>8032</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D23" s="2">
         <v>20000</v>
@@ -2198,10 +2474,10 @@
         <v>8041</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D24" s="2">
         <v>10000</v>
@@ -2221,10 +2497,10 @@
         <v>8042</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D25" s="2">
         <v>20000</v>
@@ -2244,10 +2520,10 @@
         <v>9011</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D26" s="2">
         <v>50000</v>
@@ -2267,10 +2543,10 @@
         <v>9021</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D27" s="2">
         <v>50000</v>
@@ -2291,33 +2567,748 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="7" priority="6">
       <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="6" priority="7">
       <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="110.125" customWidth="1"/>
+    <col min="5" max="5" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>10001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>10002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>10003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>10004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>10005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>10006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>10007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>10008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>10009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10011</v>
+      </c>
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>10012</v>
+      </c>
+      <c r="B12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>10013</v>
+      </c>
+      <c r="B13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>10014</v>
+      </c>
+      <c r="B14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>10014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>10014</v>
+      </c>
+      <c r="B16" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>10014</v>
+      </c>
+      <c r="B17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>10014</v>
+      </c>
+      <c r="B18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>10014</v>
+      </c>
+      <c r="B19" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>10014</v>
+      </c>
+      <c r="B20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>10014</v>
+      </c>
+      <c r="B21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" t="s">
+        <v>153</v>
+      </c>
+      <c r="E21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>10014</v>
+      </c>
+      <c r="B22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>10014</v>
+      </c>
+      <c r="B23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" t="s">
+        <v>155</v>
+      </c>
+      <c r="E23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>10014</v>
+      </c>
+      <c r="B24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>10014</v>
+      </c>
+      <c r="B25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>10014</v>
+      </c>
+      <c r="B26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>10014</v>
+      </c>
+      <c r="B27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" t="s">
+        <v>161</v>
+      </c>
+      <c r="E27" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>10014</v>
+      </c>
+      <c r="B28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" t="s">
+        <v>162</v>
+      </c>
+      <c r="E28" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>10014</v>
+      </c>
+      <c r="B29" t="s">
+        <v>146</v>
+      </c>
+      <c r="C29" t="s">
+        <v>147</v>
+      </c>
+      <c r="D29" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>10014</v>
+      </c>
+      <c r="B30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E30" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>10014</v>
+      </c>
+      <c r="B31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>10014</v>
+      </c>
+      <c r="B32" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>10014</v>
+      </c>
+      <c r="B33" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>10014</v>
+      </c>
+      <c r="B34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E34" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>10014</v>
+      </c>
+      <c r="B35" t="s">
+        <v>146</v>
+      </c>
+      <c r="C35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>10014</v>
+      </c>
+      <c r="B36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" t="s">
+        <v>170</v>
+      </c>
+      <c r="E36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>10014</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>10014</v>
+      </c>
+      <c r="B38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" t="s">
+        <v>172</v>
+      </c>
+      <c r="E38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>10014</v>
+      </c>
+      <c r="B39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>10014</v>
+      </c>
+      <c r="B40" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" t="s">
+        <v>174</v>
+      </c>
+      <c r="E40" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>10014</v>
+      </c>
+      <c r="B41" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2337,13 +3328,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2352,10 +3343,10 @@
         <v>ItemID</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2363,10 +3354,10 @@
         <v>ItemName</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2374,10 +3365,10 @@
         <v>ItemType</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2385,10 +3376,10 @@
         <v>BasicPrice</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2396,10 +3387,10 @@
         <v>Stack</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2407,10 +3398,10 @@
         <v>StoragePeriod</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2451,16 +3442,16 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -2693,7 +3684,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>OR($C1="Seed",$C1="Material")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2714,13 +3705,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2729,10 +3720,10 @@
         <v>ItemID</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2740,10 +3731,10 @@
         <v>ItemName</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2751,10 +3742,10 @@
         <v>ItemType</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2762,10 +3753,10 @@
         <v>PriceStdDev</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2773,10 +3764,10 @@
         <v>BasicPrice</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2784,10 +3775,10 @@
         <v>GrowthTime</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -2795,10 +3786,10 @@
         <v>MaxYield</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -2806,10 +3797,10 @@
         <v>MinYield</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -2817,10 +3808,10 @@
         <v>WaterConsumption</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2872,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -2889,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -2906,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -2923,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -2940,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -2957,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -2974,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -2991,7 +3982,7 @@
         <v>201</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -3008,7 +3999,7 @@
         <v>202</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -3093,7 +4084,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -3110,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -3127,7 +4118,7 @@
         <v>302</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -3144,7 +4135,7 @@
         <v>302</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -3161,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -3178,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -3187,13 +4178,13 @@
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A2:A20">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(A2 &gt; 300, A2 &lt; 400)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(A2 &gt; 200, A2 &lt; 300)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND(A2 &gt; 100, A2 &lt; 200)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3204,103 +4195,185 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="6.75" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="2" max="3" width="13.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.75" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="H1" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="E2" s="3">
         <v>5</v>
       </c>
-      <c r="D2" s="3">
+      <c r="F2" s="3">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="3">
         <v>10000</v>
       </c>
-      <c r="C3" s="3">
+      <c r="E3" s="3">
         <v>20</v>
       </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="F3" s="3">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3">
         <v>4</v>
       </c>
-      <c r="F3" s="3">
+      <c r="H3" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="3">
         <v>20000</v>
       </c>
-      <c r="C4" s="3">
-        <v>40</v>
-      </c>
-      <c r="D4" s="3">
-        <v>5</v>
-      </c>
       <c r="E4" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>6</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>32</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>3</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="9" priority="1">
+  <conditionalFormatting sqref="B1:B4 A5:A1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>Prototype</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3310,134 +4383,220 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715291B3-9102-4FF1-A4AF-13D65BEE1B70}">
-  <dimension ref="A1:F13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A11">TRANSPOSE(ObjectDataTable!A1:J1)</f>
+        <v>ObjectID</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>ObjectName</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>ObjectType</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>Price</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>MainInv</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>SubInv</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>Speed</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>WorkDuration</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>ProductionAmount</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <v>UseToDemo</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F6">
-    <sortCondition descending="1" ref="B2:B6"/>
-  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B13">
-    <cfRule type="expression" dxfId="8" priority="1">
-      <formula>Prototype</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E772BBA4-8366-43B3-9824-1E271127840B}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.75" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>900</v>
+      </c>
+      <c r="B2" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ECB86C-D64A-46E1-8165-2F7D3A7C7284}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A3">TRANSPOSE(ConfigurationDataTable!A1:B1)</f>
+        <v>GameDayDuration</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>TutorialEnabled</v>
+      </c>
+      <c r="B3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276CF695-9D11-4887-BDD3-E0C8B8D5DBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB341AA4-3084-43E4-906C-D54FB88FC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="6" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="5250" yWindow="1665" windowWidth="21600" windowHeight="11295" tabRatio="890" activeTab="6" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
     <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
-    <sheet name="ProductDataTable" sheetId="3" r:id="rId3"/>
-    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId4"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId5"/>
-    <sheet name="ObjectDataTable" sheetId="5" r:id="rId6"/>
-    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId7"/>
-    <sheet name="ConfigurationDataTable" sheetId="9" r:id="rId8"/>
-    <sheet name="ConfigurationDataTable_Meta" sheetId="10" r:id="rId9"/>
-    <sheet name="ScenarioDataTable" sheetId="11" r:id="rId10"/>
+    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId3"/>
+    <sheet name="ProductDataTable" sheetId="3" r:id="rId4"/>
+    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId5"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId6"/>
+    <sheet name="ObjectDataTable" sheetId="5" r:id="rId7"/>
+    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId8"/>
+    <sheet name="ConfigurationDataTable" sheetId="9" r:id="rId9"/>
+    <sheet name="ConfigurationDataTable_Meta" sheetId="10" r:id="rId10"/>
+    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="336">
   <si>
     <t>ItemID</t>
   </si>
@@ -572,191 +573,11 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>TargetUI</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Player</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_StoryTelling_TextBox</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI_Chat_TextBox</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>….{PlayerName}님 괜찮으신가요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>음, 로딩이 아직 덜 됐나.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>3, 2, 1, {PlayerName}님. 눈을 떠 보시겠어요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아 다행이네요, 무사히 투영된 것 같아서.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오, 성공했다고 보면 되나요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우선 반쪽짜리 성공이라고 보시면 되겠네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>저희 프로젝트는 이제 시작이라고 봐야 하겠지만, 시작이 반이다 뭐 그런 말이 있잖아요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>… 그럼 우선 뭐 부터 해야 할까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">그 슈트에 대한 조작법부터 간단히 알려드리도록 할게요. </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>좋아요. 원하는 위치로 이동하고 싶다면 지금처럼 하시면 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금 화면에 밝게 빛나는 타일에 우클릭을 해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음으로 창고 건물에 좌클릭을 해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Category</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Tutorial_Basic</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>루크</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘했어요. 건물이나 NPC들에게 좌클릭을 하면 인터페이스가 뜨는 등의 상호작용을 할 수 있어요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>반대로 창고에 아이템을 넣고 싶다면 똑같이 더블 클릭하거나 창고 슬롯으로 드래그 하면 되죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자. 이제 창고에서 볼일은 끝났으니 나가볼까요? 나가는 버튼은 많이 익숙하실 것 같네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>… 천천히 알려드릴테니 재촉하진 말아주세요…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우측 하단에 표시한 버튼을 눌러보시겠어요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>네 잘하셨어요. 그 버튼을 누르시면 건축 모드로 들어가게 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 모드에서는 다른 오브젝트들이 전부 블러 처리가 되어서 건축을 할 때 도움이 되실 겁니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 아래에 밭을 눌러보시면 밭에 대한 정보도 볼 수 있고, 마우스 포인터 위치에 따른 프리뷰도 보실 수 있답니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>원하시는 위치에 밭을 설치해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘하셨어요. 이제 종료 버튼을 누르시면 건축 모드를 종료하실 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>창고에 있는 씨감자를 더블 클릭하거나 하단 인벤토리 왼쪽 칸에 드래그하면 아이템을 꺼낼 수 있답니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>감자를 꺼내긴 했는데 잔디밭에 그냥 묻을 수도 없고… 밭을 만들거나 하는 방법은요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>드디어 이 행성에서의 첫 농사를 시작할 수 있겠네요!</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잠깐, 그런데 밭에 물은 안 줘도 괜찮나요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그럴리가요. 지구에서 자랐던 식물인데 물은 당연히 필요하죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 창고 옆에 있는 "하이드로 리엑터"에 우클릭해서 이동해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>보조 인벤토리에 물병 아이템이 생긴게 보이죠? 물병을 얻으려면 꼭 하이드로 리엑터에 우클릭을 해야 합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 {2}번 키를 눌러서 물병을 사용할 준비를 해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그 상태로 밭에 상호작용을 하면 물병의 물을 사용해서 밭에 수분을 공급할 수 있답니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수분은 작물이 성장할 때 마다 일정량이 소모되고, 수분이 부족하면 성장이 멈추게 되니 밭의 수분량을 꼭 신경쓰세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 {1번} 키를 눌러서 씨감자 봉지를 사용해볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 밭의 각 칸에 상호작용을 해서 감자를 모두 심어보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘했습니다. 이제 감자가 다 자랄 때 까지 기다리시면 되는데... 기다리기엔 시간이 없으니 이번에는 바로 자란 시점으로 가볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>다 자란 감자에도 똑같이 상호작용을 하시면 수확을 하실 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수확한 감자는 가운데에 메인 인벤토리에 저장이 됩니다. 이 아이템도 씨앗처럼 창고에 저장할 수 있죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>특히 창고에 저장하지 않고 들고 다니면 작물이 더 빠르게 썩을 수 있으니 되도록 바로 창고에 넣는걸 추천드립니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그러면 이걸 팔면 전부 제 돈인거죠? 그런데 이걸 팔려면 본부까지 보내야 할텐데…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>걱정하지 마세요. 창고에 다시 한 번 상호작용 해보시겠어요?</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -809,6 +630,773 @@
   </si>
   <si>
     <t>데모버전 사용 여부</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아가레아산 당근이 눈 건강에 탁월하다는 연구 결과가 발표되었습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Empty</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>안녕하세요. 프로토타입 오토팜의 담당자 루크입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어님의 쾌적하고 안전한 아가레아 생활을 위해 각종 수칙들을 설명드리도록 하겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">튜토리얼을 진행하시겠다면 Go, 바로 게임으로 들어가시겠다면 Skip을 눌러주세요. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이미 잘 아시는 것 같군요. 지금 부터 자유롭게 게임을 즐겨주시면 되겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도 혹시 모르니 튜토리얼이 필요하실 땐 알림 버튼을 눌러서 튜토리얼 진행하기를 선택해주세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Basic_BIC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial_BIC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러면 우선 슈트 조작 방법을 설명드리겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에 반짝이는 타일에 우클릭을 해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 좌측으로 두 칸 떨어진 위치의 타일에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금처럼 원하는 타일에 우클릭을 하면 그 위치로 이동을 할 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음으로 반짝이는 건물에 좌클릭을 해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>원하는 건물이나 캐릭터에 좌클릭을 하면 상호작용을 할 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용을 하면 지금처럼 오브젝트의 인터페이스가 등장하며 관련된 작업을 할 수 있죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 물탱크에 좌클릭을 해서 물병을 얻어볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>물탱크에 클릭 표시</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>만약 보조 인벤토리가 가득 차 있다면 물탱크를 눌러도 물병을 얻을 수 없으니 조심하세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 전지를 충전해봅시다. 오른 쪽 하단 슬롯에 있는 아이템을 더블 클릭하거나 표시된 영역에 드래그해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전 슬롯 첫 번째 칸에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수소 전지라는 이름 답게 물을 분해해서 얻은 수소를 채워 넣는 방식으로 충전을 시키죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>일일이 단자에 충전시키는 것이 번거롭다면 자동 충전 토글이나 일괄 충전 버튼을 눌러보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전이 끝나면 자동으로 메인 창고로 이동을 하니 과충전으로 인한 사고는 걱정 안하셔도 되겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 이 곳에서의 볼일은 끝났으니 나가볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXIT버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제는 일을 시작할 시간입니다. 밭을 먼저 설치해야겠죠?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>건설 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>방금 누르신 버튼은 건축 모드로 들어가는 버튼입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축 모드에서는 건물을 제외한 다른 캐릭터 오브젝트는 비활성화 처리가 되고, 타일의 그리드가 강조됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭을 한 번 눌러보시겠어요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 "밭" 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭을 포함한 원하는 건물을 선택하면 왼 쪽에 그 건물의 크기와 보유하고 있는 건물 키트의 개수를 확인할 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭 같은 경우는 단순히 땅을 갈기만 하면 되기 때문에 키트는 필요 없이 무한으로 표시가 되죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자 그러면 표시된 영역에 밭을 설치해 볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭 설치 영역에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>건물 "축사"버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 원하는 위치에 설치를 해보세요. 밭이나 이미 다른 건물이 있는 위치에는 설치하지 못합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라는 캐릭터를 따라가지 않습니다. 커서를 화면 끝으로 이동시키면 그 방향으로 이동하죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘 하셨습니다. 이번에는 소를 키울 축사도 하나 만들어 볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>축사 같이 키트를 소모해야 하는 건물은 설치한 영역에 부지가 먼저 생성이 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금처럼 키트가 있는 경우에는 즉시 설치가 진행이 되지만, 키트가 없다면 구매를 해서 수령할 때 까지 기다려야 하죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 건축 모드를 종료해보죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>건축 모드 종료 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보조 인벤토리 1번 슬롯에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 밭에서 일하는 방법을 알려드리겠습니다. {1번} 키를 누르거나 슬롯을 클릭해서 씨감자를 사용할 준비를 해볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 빈 밭에 한 칸 씩 상호작용해서 심어봅시다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>심을 때 마다 한 칸 씩 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘 하셨습니다. 감자가 자라는 시간은 하루 정도 걸리긴 하지만… 이번만 빠르게 시간을 돌려볼게요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자, 다 자란 감자들을 하나 씩 클릭해서 수확해보죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 감자를 바로 성장시키기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확할 때 마다 한 칸 씩 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확한 아이템들은 모두 가운데에 있는 슬롯에 저장됩니다. 메인 인벤토리라고 부르죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 창고 건물에 상호작용을 해볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 창고 건물에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템을 모두 저장하거나 꺼낼 때는 방금 처럼 하시면 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>꺼낼 아이템에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확한 감자를 더블 클릭하거나 창고에 드래그해서 저장해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자 아이템에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>적재 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 낱개로 꺼내볼까요? Ctrl키를 누른 채로 당근 씨앗을 좌클릭해서 꺼내보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 수확한 감자를 팔아봅시다. 적재 버튼을 눌러보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>적재 모드에서는 창고와의 상호작용이 모두 우주선에서 이루어진다 생각하시면 되겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그러면 감자를 더블 클릭하거나 우주선 슬롯에 드래그해서 적재를 해봅시다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고에 있는 감자에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우주선에 적재를 하면 현재 가격에 따른 정산 금액이 표시됩니다. 오늘은 감자 가격이 조금 오른 편이군요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정산 금액 Panel에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 우주선 출발 준비를 시켜볼까요? 적재 완료 버튼을 눌러보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>적재 완료 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우주선은 다음 날 자정에 출발을 합니다. 그래서 전날 23시부터는 출발을 위해 적재 버튼이 비활성화 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 빠른 판매를 위해 시간을 조금 돌려 볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다음 날 오전 8시로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그런데 오전 9시가 되면 아이템들의 가격이 변하기 때문에 가격 변동 추이도 확인을 해봐야 하겠습니다. 마침 오늘은 월요일이기도 하네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 데이터 패널 버튼을 눌러보세요. {C}키를 누르셔도 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 패널 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>앞으로 플레이어님이 많이 보게 되실 데이터 패널 화면입니다. 판매할 수 있는 아이템들의 가격이 어떻게 변했는지 볼 수 있죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>저희가 팔았던 감자의 가격 변동을 한 번 볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자 아이템 정보 Panel에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 화면에서는 일 주일 간의 가격 변동 추이를 차트로 볼 수 있는 화면입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘의 감자 값은 떨어졌네요. 어제 올랐을 때 팔아서 정말 다행입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 오늘은 월요일이기 때문에 아이템들에 대한 뉴스가 나오는 날입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴스에 따라 아이템 가격이 크게 오르거나 떨어지기 때문에 꼭 확인을 하는 것이 중요하죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉴스 인덱스 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그에 비해 당근은 가격이 오르는 호재가 나온 상황입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>마침 창고에 당근 씨앗을 준비해뒀었는데, 오히려 잘 되었네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래도 부족할 수 있으니 우주선이 돌아오기 전에 상점에서 조금 주문을 해볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상점 데이터 칩에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 패널 화면에서는 데이터 칩을 눌러서 화면을 전환할 수 있습니다. 상점 같은 경우는 S를 눌러도 되죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템의 종류에 따라 씨앗, 로봇, 부품, 건축 키트 메뉴가 나뉘어져 구성되어 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우선 당근 씨앗부터 구매를 해볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근 씨앗 구매 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매 수량은 +버튼을 누르거나 숫자칸을 클릭해 직접 입력해서 정할 수 있습니다. 우선 50개만 구매 해볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자 칸에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇 메뉴 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 축사에서 키울 소랑 우유를 담을 병도 구매를 해봅시다. 우선 소 부터 한 마리 구매해보죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자동 스크롤 및 소 구매 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>소는 지구를 떠난 이후부터 상당히 비싼 몸값이 되었죠. 그래도 첫 정착인 만큼 한 마리는 무상 지원을 해드리기로 했습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매 확정 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>대신 빈 병은 직접 구매해주세요. 넉넉하게 20개만 구매해보죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈 병 20개 구매 네비게이팅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자 이번에는 플레이어님을 대신해서 자동으로 일해 줄 로봇을 구매해봅시다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 당장은 프로토타입 버전 뿐이지만… 앞으로 좋은 결과가 있을거라 생각되네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로토타입 구매 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로토타입도 소와 마찬가지로 초기 정착 지원 형태로 두 기를 무상 지원해드리겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로토타입 두 기 구매 네비게이팅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매한 아이템들은 우주선이 복귀할 때 실어서 같이 배송되기 때문에 우주선이 복귀하기 전에 구매를 끝마치는게 중요하죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>모두 구매를 하니 12시가 되어가는군요. 곧 우주선이 출발할 시간입니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>만약 우주선이 출발한 이후에 주문을 하면 우주선을 다시 보내야 수령할 수 있는 것이죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇다고 한 번 살 때 너무 많이 구매를 하면 우주선에 모두 실을 수 없기 때문에 이 부분도 조심 하셔야겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자 이제 우주선이 도착한 것 같네요. 도착한 로봇들에게도 일을 시켜 볼까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇 관리 데이터 칩에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금은 모든 로봇이 일을 안하고 있어서 자고 있는 모습이네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 화면에서는 보유 중인 모든 자동화 로봇의 정보를 보거나 이름을 바꿔줄 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 번째 로봇에 이름 칸에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 번째 로봇의 이름을 한 번 바꿔볼까요? 원하는 이름 아무거나 지어주세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{input}. 좋은 이름이네요. 이제 명령 하달을 위해 프로토타입의 인터페이스로 들어가보죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>첫 번째 로봇 칸에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>각각의 로봇 인터페이스는 지금처럼 로봇 관리 패널로 들어오거나 필드의 로봇에게 직접 상호작용을 해서 들어올 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>화면에 표시된 곳을 누르고 설치했던 밭을 클릭해 보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 구역 버튼에 반짝이는 효과, 이후에 필드 밭에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇 한 기는 밭 4개까지 담당해서 일을 할 수 있습니다. 물론 다른 로봇들에게도 같은 밭을 담당시킬 수 있지만, 효율적이진 않죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 구역을 할당했으니, 이제는 어떤 것을 생산할지 명령해야겠죠? 이번에는 당근을 심도록 해봅시다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>생산 아이템 버튼에 반짝이는 효과, 이후 목록에 당근에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 로봇이 스스로 일을 하는 모습이 보이죠? 로봇은 움직이거나 일을 할 때 수소 에너지를 소모하여 물을 생산합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 사용 중인 배터리의 용량이 부족해지면 스스로 창고에서 충전된 배터리로 교체를 하기도 하죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로토타입이긴 해도 최대한 스스로 해결할 수 있도록 만들어졌으니 걱정하지 않으셔도 됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이제 다른 놀고 있는 프로토타입에게도 일을 할당해보죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 번째 로봇 오브젝트에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이번에는 축사에서 일을 시켜 봅시다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>축사 건물에 작업 구역 할당 네비게이팅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>축사에 배치를 한다면 구매했던 소들을 알아서 잘 몰아오게 됩니다. 다행히 소들이 근처에 있네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>데려온 소 들은 귀한 몸이기 때문에 축사 건물에 갖혀 있는 것이 아닌 울타리 내에서 자유롭게 풀을 뜯어 먹고 살겁니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>마실 물은 축사 건물 오른 쪽에 지하수 펌핑 장치로 확보할 수 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 위치 지하수 펌핑 장치로 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 위치 두 번째 로봇 위치로 원상복귀</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>축사는 밭과 달리 하나의 축사에서만 작업이 가능한 것도 기억해주세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>축사에 배치된 소에게 카메라 이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정 부족한 물은 로봇이 생산하는 수분으로도 충분히 해결할 수 있습니다. 덕분에 축사에서 일하는 로봇은 물을 분출할 일이 없죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>마지막으로 로봇의 업그레이드에 관한 것을 알려드리겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇 업그레이드 메뉴 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 프로토타입의 성능은 상당히 좋지 못한 편입니다. 이동속도부터 작업 효율까지 모든 면에서 말이죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>기체 자체를 업그레이드할 수는 없지만, 업그레이드 퍽을 장착하여 성능을 조금 올릴 수 있죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>제가 미리 적재해둔 속도 업그레이드 부품이 아이템 슬롯에 보이죠? 더블 클릭을 하거나 맞는 위치에 드래그해서 장착해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>속도 부품에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>확실히 로봇의 이동 속도가 빨라졌네요. 아직 연구 중인 로봇이기 때문에 성능에 한계는 있지만… 열심히 개발해보겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>여기까지 튜토리얼을 마치도록 하겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>알림 버튼에 반짝이는 효과</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>남은 목표는 더 많은 프로토타입을 이용한 자동화 농장을 운영하며 매일 가격이 변화하는 시장에서 1억을 목표로 달려봅시다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial_Basic_End</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial_BIC_Skip</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial_BIC_Manual</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tutorial_BIC_HDR</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 감자 가격이 조금 떨어진 이유가 악재 때문이었네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우주선이 출발했고, 08시가 되면 정산된 금액이 입금됩니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>어제는 평소보다 가격이 조금 올랐는데, 곧 09시니 가격이 어떻게 변할지 궁금하긴 하네요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>물병은 사용할 수 있는 아이템이기 때문에 왼 쪽에 3칸짜리 인벤토리에 생성됩니다. 보조 인벤토리라고 부르죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금 화면은 하이드로 리엑터라고 하는 건물의 인터페이스입니다. 수소 전지를 충전하거나 물을 얻을 수 있는 인터페이스죠.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turotial_BIC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>루크</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확을 하고 나면 밭에 수분이 조금 떨어집니다. 밭에 한 번 커서를 올려보시겠어요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭에 커서 표시</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>부족한 수분은 방금 얻은 물병의 물을 사용해서 채울 수 있습니다. 이번엔 물병을 밭에 사용해보세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭에 수분이 부족하면 작물을 심을 수 없으니 직접 작물을 기를 때는 수분량을 조심해야 합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭에 물을 주는 식으로 소모를 하긴 하지만 물이 가득 차게 된다면 잠시 작업이 중단되고 제자리에서 물을 뿜어내는 시간이 필요합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyCode</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRebindable</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mouse0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_Interaction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>좌클릭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mouse1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_Movement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우클릭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Chart</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Shop</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Robot</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Storage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Hydro</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select_Slot1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select_Slot2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select_Slot3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prototype</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cow</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cattle</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chicken</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1495,7 +2083,7 @@
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
@@ -1569,7 +2157,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="-0.24994659260841701"/>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1584,6 +2172,13 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1917,7 +2512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
@@ -2310,16 +2905,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>7011</v>
+        <v>6021</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>112</v>
+        <v>331</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>113</v>
+        <v>332</v>
       </c>
       <c r="D17" s="2">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -2333,16 +2928,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>8011</v>
+        <v>6031</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>333</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>56</v>
+        <v>334</v>
       </c>
       <c r="D18" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -2356,16 +2951,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>8012</v>
+        <v>6032</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>61</v>
+        <v>335</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>56</v>
+        <v>334</v>
       </c>
       <c r="D19" s="2">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -2379,16 +2974,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>8021</v>
+        <v>7011</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="D20" s="2">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -2402,16 +2997,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8022</v>
+        <v>8011</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D21" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -2420,21 +3015,21 @@
         <v>-1</v>
       </c>
       <c r="G21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8031</v>
+        <v>8012</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D22" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -2443,21 +3038,21 @@
         <v>-1</v>
       </c>
       <c r="G22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8032</v>
+        <v>8021</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D23" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="2">
         <v>1</v>
@@ -2466,21 +3061,21 @@
         <v>-1</v>
       </c>
       <c r="G23" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8041</v>
+        <v>8022</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D24" s="2">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E24" s="2">
         <v>1</v>
@@ -2489,21 +3084,21 @@
         <v>-1</v>
       </c>
       <c r="G24" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8042</v>
+        <v>8031</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D25" s="2">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E25" s="2">
         <v>1</v>
@@ -2512,21 +3107,21 @@
         <v>-1</v>
       </c>
       <c r="G25" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>9011</v>
+        <v>8032</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="E26" s="2">
         <v>1</v>
@@ -2535,21 +3130,21 @@
         <v>-1</v>
       </c>
       <c r="G26" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>9021</v>
+        <v>8041</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D27" s="2">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="E27" s="2">
         <v>1</v>
@@ -2561,34 +3156,106 @@
         <v>1</v>
       </c>
     </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>8042</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>9011</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G27">
-    <sortCondition ref="A2:A27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G30">
+    <sortCondition ref="A2:A30"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
+      <formula>AND($A1 &gt;= 6000, $A1 &lt; 7000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="8" priority="6">
       <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="6" priority="8">
       <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2598,717 +3265,1737 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
-  <dimension ref="A1:E41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ECB86C-D64A-46E1-8165-2F7D3A7C7284}">
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="110.125" customWidth="1"/>
-    <col min="5" max="5" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>10001</v>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A3">TRANSPOSE(ConfigurationDataTable!A1:B1)</f>
+        <v>GameDayDuration</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>10002</v>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>TutorialEnabled</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>10003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" t="s">
-        <v>147</v>
-      </c>
-      <c r="D4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>10004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>10005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>10006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>10007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" t="s">
-        <v>139</v>
-      </c>
-      <c r="E8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>10008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>10009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D10" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10011</v>
-      </c>
-      <c r="B11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C11" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>10012</v>
-      </c>
-      <c r="B12" t="s">
-        <v>146</v>
-      </c>
-      <c r="C12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" t="s">
-        <v>142</v>
-      </c>
-      <c r="E12" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>10013</v>
-      </c>
-      <c r="B13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>10014</v>
-      </c>
-      <c r="B14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>10014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" t="s">
-        <v>147</v>
-      </c>
-      <c r="D15" t="s">
-        <v>158</v>
-      </c>
-      <c r="E15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>10014</v>
-      </c>
-      <c r="B16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C16" t="s">
-        <v>147</v>
-      </c>
-      <c r="D16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>10014</v>
-      </c>
-      <c r="B17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" t="s">
-        <v>147</v>
-      </c>
-      <c r="D17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>10014</v>
-      </c>
-      <c r="B18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" t="s">
-        <v>159</v>
-      </c>
-      <c r="E18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>10014</v>
-      </c>
-      <c r="B19" t="s">
-        <v>146</v>
-      </c>
-      <c r="C19" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>10014</v>
-      </c>
-      <c r="B20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>10014</v>
-      </c>
-      <c r="B21" t="s">
-        <v>146</v>
-      </c>
-      <c r="C21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>10014</v>
-      </c>
-      <c r="B22" t="s">
-        <v>146</v>
-      </c>
-      <c r="C22" t="s">
-        <v>147</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>10014</v>
-      </c>
-      <c r="B23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" t="s">
-        <v>155</v>
-      </c>
-      <c r="E23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>10014</v>
-      </c>
-      <c r="B24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>10014</v>
-      </c>
-      <c r="B25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>10014</v>
-      </c>
-      <c r="B26" t="s">
-        <v>146</v>
-      </c>
-      <c r="C26" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" t="s">
-        <v>160</v>
-      </c>
-      <c r="E26" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>10014</v>
-      </c>
-      <c r="B27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" t="s">
-        <v>161</v>
-      </c>
-      <c r="E27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>10014</v>
-      </c>
-      <c r="B28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" t="s">
-        <v>147</v>
-      </c>
-      <c r="D28" t="s">
-        <v>162</v>
-      </c>
-      <c r="E28" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>10014</v>
-      </c>
-      <c r="B29" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" t="s">
-        <v>147</v>
-      </c>
-      <c r="D29" t="s">
-        <v>163</v>
-      </c>
-      <c r="E29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>10014</v>
-      </c>
-      <c r="B30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" t="s">
-        <v>147</v>
-      </c>
-      <c r="D30" t="s">
-        <v>164</v>
-      </c>
-      <c r="E30" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>10014</v>
-      </c>
-      <c r="B31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D31" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>10014</v>
-      </c>
-      <c r="B32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C32" t="s">
-        <v>147</v>
-      </c>
-      <c r="D32" t="s">
-        <v>166</v>
-      </c>
-      <c r="E32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>10014</v>
-      </c>
-      <c r="B33" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" t="s">
-        <v>147</v>
-      </c>
-      <c r="D33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>10014</v>
-      </c>
-      <c r="B34" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E34" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>10014</v>
-      </c>
-      <c r="B35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" t="s">
-        <v>169</v>
-      </c>
-      <c r="E35" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>10014</v>
-      </c>
-      <c r="B36" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E36" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>10014</v>
-      </c>
-      <c r="B37" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>10014</v>
-      </c>
-      <c r="B38" t="s">
-        <v>146</v>
-      </c>
-      <c r="C38" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" t="s">
-        <v>172</v>
-      </c>
-      <c r="E38" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>10014</v>
-      </c>
-      <c r="B39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" t="s">
-        <v>147</v>
-      </c>
-      <c r="D39" t="s">
-        <v>173</v>
-      </c>
-      <c r="E39" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>10014</v>
-      </c>
-      <c r="B40" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" t="s">
-        <v>130</v>
-      </c>
-      <c r="D40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>10014</v>
-      </c>
-      <c r="B41" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" t="s">
-        <v>175</v>
-      </c>
-      <c r="E41" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
+  <dimension ref="A1:F108"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="22.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="65.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>100001</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>100002</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>100003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>110001</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>110002</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>110003</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>110004</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>110005</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>110006</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>110007</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>110008</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>110009</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>110010</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>110011</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>110012</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>110013</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>110014</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>110015</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>110016</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>110017</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>110018</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>110019</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>110020</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>110021</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>110022</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>110023</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>110024</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>110025</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>110026</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>110027</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>110028</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>110029</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>110030</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>110031</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>110032</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>110033</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>110034</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>110035</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>110036</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>110037</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>110038</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>110039</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>110040</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>110041</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>110042</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>110043</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>110044</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>110045</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>110046</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>110047</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>110048</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>110049</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>110050</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>110051</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>110052</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>110053</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>110054</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>110055</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>110056</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>110057</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>110058</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>110059</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>110060</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>110061</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>110062</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>110063</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>110064</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>110065</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>110066</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>110067</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>110068</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>110069</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>110070</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>110071</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>110072</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>110073</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>110074</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>110075</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>110076</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>110077</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>110078</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>110079</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>110080</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>110081</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>110082</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>110083</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>110084</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>110085</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>110086</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>110087</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>110088</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>110089</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>110090</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>110091</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>110092</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>110093</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>110094</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>110095</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>110096</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>110097</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>110098</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>110099</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>110100</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>190001</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>190002</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>190101</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>190102</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F140">
+    <sortCondition ref="A2:A140"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3412,6 +5099,178 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D902D-6443-438F-90C7-179D093475FD}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>3</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3693,7 +5552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3820,9 +5679,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
@@ -4170,6 +6029,23 @@
       </c>
       <c r="E20" s="2" t="s">
         <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>990</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4193,7 +6069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4233,10 +6109,10 @@
         <v>48</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>111</v>
@@ -4244,7 +6120,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
-        <v>11</v>
+        <v>6011</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>49</v>
@@ -4276,7 +6152,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
-        <v>21</v>
+        <v>6021</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>50</v>
@@ -4308,7 +6184,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
-        <v>31</v>
+        <v>6031</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>120</v>
@@ -4340,10 +6216,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
-        <v>32</v>
+        <v>6032</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>123</v>
@@ -4382,7 +6258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4408,7 +6284,7 @@
         <v>ObjectID</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="C2" t="s">
         <v>80</v>
@@ -4419,7 +6295,7 @@
         <v>ObjectName</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="C3" t="s">
         <v>81</v>
@@ -4430,7 +6306,7 @@
         <v>ObjectType</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>181</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
@@ -4441,7 +6317,7 @@
         <v>Price</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="C5" t="s">
         <v>80</v>
@@ -4452,7 +6328,7 @@
         <v>MainInv</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
         <v>80</v>
@@ -4463,7 +6339,7 @@
         <v>SubInv</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="C7" t="s">
         <v>80</v>
@@ -4474,7 +6350,7 @@
         <v>Speed</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="C8" t="s">
         <v>101</v>
@@ -4485,7 +6361,7 @@
         <v>WorkDuration</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
         <v>101</v>
@@ -4496,7 +6372,7 @@
         <v>ProductionAmount</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="C10" t="s">
         <v>80</v>
@@ -4507,7 +6383,7 @@
         <v>UseToDemo</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>188</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
@@ -4519,7 +6395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E772BBA4-8366-43B3-9824-1E271127840B}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4550,53 +6426,4 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ECB86C-D64A-46E1-8165-2F7D3A7C7284}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A3">TRANSPOSE(ConfigurationDataTable!A1:B1)</f>
-        <v>GameDayDuration</v>
-      </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>TutorialEnabled</v>
-      </c>
-      <c r="B3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB341AA4-3084-43E4-906C-D54FB88FC025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F47A93-87FA-43AD-BBF8-A7C234E31F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="1665" windowWidth="21600" windowHeight="11295" tabRatio="890" activeTab="6" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="335">
   <si>
     <t>ItemID</t>
   </si>
@@ -1384,19 +1384,15 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Robot</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Cow</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>Cattle</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Chicken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2911,7 +2907,7 @@
         <v>331</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D17" s="2">
         <v>10000</v>
@@ -2931,7 +2927,7 @@
         <v>6031</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>334</v>
@@ -2954,7 +2950,7 @@
         <v>6032</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>334</v>

--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F47A93-87FA-43AD-BBF8-A7C234E31F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA15D17-C2F9-4D23-A987-5231B8D38473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="356">
   <si>
     <t>ItemID</t>
   </si>
@@ -1292,10 +1292,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>KeyCode</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ActionType</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1312,10 +1308,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>좌클릭</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Mouse1</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1324,10 +1316,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>우클릭</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>C</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -1393,6 +1381,102 @@
   </si>
   <si>
     <t>Object</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultKeyCode</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interaction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description_KR</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>차트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상점</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇 관리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이드로 리엑터</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modifier1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modifier2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Setting</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Escape</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2904,10 +2988,10 @@
         <v>6021</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="D17" s="2">
         <v>10000</v>
@@ -2927,10 +3011,10 @@
         <v>6031</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D18" s="2">
         <v>20000</v>
@@ -2950,10 +3034,10 @@
         <v>6032</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D19" s="2">
         <v>5000</v>
@@ -5096,171 +5180,333 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D902D-6443-438F-90C7-179D093475FD}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="15.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="15.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="E3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E5" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>42</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>1</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="C12" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D12" s="2">
         <v>3</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1</v>
+      <c r="E12" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H13">
+    <sortCondition ref="A2:A13"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA15D17-C2F9-4D23-A987-5231B8D38473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA2A848-99C5-4DBB-99DE-0AABE9603FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,7 @@
     <sheet name="EventDataTable" sheetId="4" r:id="rId6"/>
     <sheet name="ObjectDataTable" sheetId="5" r:id="rId7"/>
     <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId8"/>
-    <sheet name="ConfigurationDataTable" sheetId="9" r:id="rId9"/>
-    <sheet name="ConfigurationDataTable_Meta" sheetId="10" r:id="rId10"/>
-    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId11"/>
+    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="357">
   <si>
     <t>ItemID</t>
   </si>
@@ -513,26 +511,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>GameDayDuration</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>인게임 하루 주기(분)</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TutorialEnabled</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>boolean</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>튜토리얼 On/Off</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>ObjectID</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -565,22 +543,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>SynarioID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Speaker</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Category</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>루크</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Chicken</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -633,850 +595,721 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>아가레아산 당근이 눈 건강에 탁월하다는 연구 결과가 발표되었습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Empty</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>TargetUI</t>
+  </si>
+  <si>
+    <t>ActionType</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsRebindable</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mouse0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_Interaction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mouse1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC_Movement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Chart</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Shop</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Robot</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Storage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Hydro</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select_Slot1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select_Slot2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select_Slot3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prototype</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cow</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chicken</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Object</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultKeyCode</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Movement</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interaction</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description_KR</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>차트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상점</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>로봇 관리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>창고</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>하이드로 리엑터</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3번 슬롯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionName</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modifier1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modifier2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopUp_Setting</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Escape</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>SynarioID</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Speaker</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Basic_BIC</t>
+  </si>
+  <si>
+    <t>루크</t>
   </si>
   <si>
     <t>안녕하세요. 프로토타입 오토팜의 담당자 루크입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>플레이어님의 쾌적하고 안전한 아가레아 생활을 위해 각종 수칙들을 설명드리도록 하겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>TargetUI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">튜토리얼을 진행하시겠다면 Go, 바로 게임으로 들어가시겠다면 Skip을 눌러주세요. </t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>튜토리얼을 진행하시겠다면 Go, 바로 게임으로 들어가시겠다면 Skip을 눌러주세요.</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_Manual</t>
+  </si>
+  <si>
+    <t>그러면 우선 슈트 조작 방법을 설명드리겠습니다.</t>
+  </si>
+  <si>
+    <t>화면에 반짝이는 타일에 우클릭을 해보세요.</t>
+  </si>
+  <si>
+    <t>플레이어 좌측으로 두 칸 떨어진 위치의 타일에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>지금처럼 원하는 타일에 우클릭을 하면 그 위치로 이동을 할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>카메라는 캐릭터를 따라가지 않습니다. 커서를 화면 끝으로 이동시키면 그 방향으로 이동하죠.</t>
+  </si>
+  <si>
+    <t>다음으로 반짝이는 건물에 좌클릭을 해보세요.</t>
+  </si>
+  <si>
+    <t>원하는 건물이나 캐릭터에 좌클릭을 하면 상호작용을 할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>상호작용을 하면 지금처럼 오브젝트의 인터페이스가 등장하며 관련된 작업을 할 수 있죠.</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_HDR</t>
+  </si>
+  <si>
+    <t>지금 화면은 하이드로 리엑터라고 하는 건물의 인터페이스입니다. 수소 전지를 충전하거나 물을 얻을 수 있는 인터페이스죠.</t>
+  </si>
+  <si>
+    <t>물탱크에 클릭 표시</t>
+  </si>
+  <si>
+    <t>우선 물탱크에 좌클릭을 해서 물병을 얻어볼까요?</t>
+  </si>
+  <si>
+    <t>물병은 사용할 수 있는 아이템이기 때문에 왼 쪽에 3칸짜리 인벤토리에 생성됩니다. 보조 인벤토리라고 부르죠.</t>
+  </si>
+  <si>
+    <t>만약 보조 인벤토리가 가득 차 있다면 물탱크를 눌러도 물병을 얻을 수 없으니 조심하세요.</t>
+  </si>
+  <si>
+    <t>충전 슬롯 첫 번째 칸에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이번에는 전지를 충전해봅시다. 오른 쪽 하단 슬롯에 있는 아이템을 표시된 영역에 드래그해보세요.</t>
+  </si>
+  <si>
+    <t>수소 전지라는 이름 답게 물을 분해해서 얻은 수소를 채워 넣는 방식으로 충전을 시키죠.</t>
+  </si>
+  <si>
+    <t>충전이 끝나면 자동으로 해제가 되니 과충전 걱정은 안하셔도 되겠습니다.</t>
+  </si>
+  <si>
+    <t>일일이 단자에 충전시키는 것이 번거롭다면 자동 충전 토글이나 일괄 충전 버튼을 눌러보세요.</t>
+  </si>
+  <si>
+    <t>자동/일괄 충전 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이제 이 곳에서의 볼일은 끝났으니 나가볼까요?</t>
+  </si>
+  <si>
+    <t>EXIT버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_Build</t>
+  </si>
+  <si>
+    <t>이제는 일을 시작할 시간입니다. 밭을 먼저 설치해야겠죠?</t>
+  </si>
+  <si>
+    <t>건설 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>방금 누르신 버튼은 건축 모드로 들어가는 버튼입니다.</t>
+  </si>
+  <si>
+    <t>건축 모드에서는 건물을 제외한 다른 캐릭터 오브젝트는 비활성화 처리가 됩니다.</t>
+  </si>
+  <si>
+    <t>밭을 한 번 눌러보시겠어요?</t>
+  </si>
+  <si>
+    <t>건물 "밭" 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>밭을 포함한 원하는 건물을 선택하면 왼 쪽에 그 건물의 크기와 보유하고 있는 건물 키트의 개수를 확인할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>밭 같은 경우는 단순히 땅을 갈기만 하면 되기 때문에 키트는 필요 없이 무한으로 표시가 되죠.</t>
+  </si>
+  <si>
+    <t>자 그러면 표시된 영역에 밭을 설치해 볼까요?</t>
+  </si>
+  <si>
+    <t>밭 설치 영역에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>잘 하셨습니다. 이번에는 소를 키울 축사도 하나 만들어 볼까요?</t>
+  </si>
+  <si>
+    <t>건물 "축사"버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이번에는 원하는 위치에 설치를 해보세요. 밭이나 이미 다른 건물이 있는 위치에는 설치하지 못합니다.</t>
+  </si>
+  <si>
+    <t>축사 같이 키트를 소모해야 하는 건물은 설치한 영역에 부지가 먼저 생성이 됩니다.</t>
+  </si>
+  <si>
+    <t>지금처럼 키트가 있는 경우에는 즉시 설치가 진행이 되지만, 키트가 없다면 구매를 해서 수령할 때 까지 기다려야 하죠.</t>
+  </si>
+  <si>
+    <t>이제 건축 모드를 종료해보죠.</t>
+  </si>
+  <si>
+    <t>건축 모드 종료 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_PC_Work</t>
+  </si>
+  <si>
+    <t>먼저 밭에서 일하는 방법을 알려드리겠습니다. {1번} 키를 누르거나 슬롯을 클릭해서 씨감자를 사용할 준비를 해볼까요?</t>
+  </si>
+  <si>
+    <t>보조 인벤토리 1번 슬롯에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이제 빈 밭에 한 칸 씩 상호작용해서 심어봅시다.</t>
+  </si>
+  <si>
+    <t>심을 때 마다 한 칸 씩 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>잘 하셨습니다. 감자가 자라는 시간은 하루 정도 걸리긴 하지만… 이번만 빠르게 시간을 돌려볼게요.</t>
+  </si>
+  <si>
+    <t>모든 감자를 바로 성장시키기</t>
+  </si>
+  <si>
+    <t>자, 다 자란 감자들을 하나 씩 클릭해서 수확해보죠.</t>
+  </si>
+  <si>
+    <t>수확할 때 마다 한 칸 씩 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>수확한 아이템들은 모두 가운데에 있는 슬롯에 저장됩니다. 메인 인벤토리라고 부르죠.</t>
+  </si>
+  <si>
+    <t>처음 밭을 만들 때는 수분이 가득했지만, 한 번 수확을 마치면 밭이 마르게 됩니다.</t>
+  </si>
+  <si>
+    <t>부족한 수분은 방금 얻은 물병의 물을 사용해서 채울 수 있습니다. 이번엔 물병을 밭에 사용해보세요.</t>
+  </si>
+  <si>
+    <t>마른 밭에는 작물을 심을 수 없기 때문에 심기 전에 물병으로 밭을 충분히 적셔줘야 합니다.</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_Storage</t>
+  </si>
+  <si>
+    <t>이제 창고 건물에 상호작용을 해볼까요?</t>
+  </si>
+  <si>
+    <t>메인 창고 건물에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>수확한 감자를 창고에 드래그해서 저장해보세요.</t>
+  </si>
+  <si>
+    <t>감자 아이템에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>아이템을 저장하거나 꺼낼 때는 방금 처럼 하시면 됩니다.</t>
+  </si>
+  <si>
+    <t>이제 수확한 감자를 팔아봅시다. 적재 버튼을 눌러보세요.</t>
+  </si>
+  <si>
+    <t>적재 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>적재 모드에서는 창고와의 상호작용이 모두 우주선에서 이루어진다 생각하시면 되겠습니다.</t>
+  </si>
+  <si>
+    <t>그러면 감자를 더블 클릭하거나 우주선 슬롯에 드래그해서 적재를 해봅시다.</t>
+  </si>
+  <si>
+    <t>창고에 있는 감자에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>우주선에 적재를 하면 상품의 현재 가격에 따른 정산 금액이 표시됩니다. 오늘은 감자 가격이 조금 오른 편이군요.</t>
+  </si>
+  <si>
+    <t>정산 금액 Panel에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이제 우주선 출발 준비를 시켜볼까요? 적재 완료 버튼을 눌러보세요.</t>
+  </si>
+  <si>
+    <t>적재 완료 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>우주선은 다음 날 자정에 출발을 합니다. 그래서 전날 23시부터는 출발을 위해 적재 버튼이 비활성화 됩니다.</t>
+  </si>
+  <si>
+    <t>빠른 정산을 위해 시간을 조금 돌려 볼까요?</t>
+  </si>
+  <si>
+    <t>다음 날 오전 8시로 이동</t>
+  </si>
+  <si>
+    <t>자정에 우주선이 출발했고, 08시가 되면 정산된 금액이 입금됩니다.</t>
+  </si>
+  <si>
+    <t>그런데 오전 9시가 되면 아이템들의 가격이 변하기 때문에 가격 변동 추이도 확인을 해봐야 하겠습니다. 마침 오늘은 월요일이기도 하네요.</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_PopUp</t>
+  </si>
+  <si>
+    <t>이번에는 데이터 패널 버튼을 눌러보세요. {C}키를 누르셔도 됩니다.</t>
+  </si>
+  <si>
+    <t>데이터 패널 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>앞으로 플레이어님이 많이 보게 되실 데이터 패널 화면입니다. 판매할 수 있는 아이템들의 가격이 어떻게 변했는지 볼 수 있죠.</t>
+  </si>
+  <si>
+    <t>저희가 팔았던 감자의 가격 변동을 한 번 볼까요?</t>
+  </si>
+  <si>
+    <t>감자 아이템 정보 Panel에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이 화면에서는 일 주일 간의 가격 변동 추이를 차트로 볼 수 있는 화면입니다.</t>
+  </si>
+  <si>
+    <t>어제는 평소보다 가격이 조금 올랐는데, 곧 09시니 가격이 어떻게 변할지 궁금하긴 하네요.</t>
+  </si>
+  <si>
+    <t>오늘의 감자 값은 떨어졌네요. 어제 올랐을 때 팔아서 정말 다행입니다.</t>
+  </si>
+  <si>
+    <t>그리고 오늘은 월요일이기 때문에 아이템들에 대한 뉴스가 나오는 날입니다.</t>
+  </si>
+  <si>
+    <t>뉴스에 따라 아이템 가격이 크게 오르거나 떨어지기 때문에 꼭 확인을 하는 것이 중요하죠.</t>
+  </si>
+  <si>
+    <t>뉴스 인덱스 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>오늘 감자 가격이 조금 떨어진 이유가 악재 때문이었네요.</t>
+  </si>
+  <si>
+    <t>그에 비해 당근은 가격이 오르는 호재가 나온 상황입니다.</t>
+  </si>
+  <si>
+    <t>마침 창고에 당근 씨앗을 준비해뒀었는데, 잘 됐네요.</t>
+  </si>
+  <si>
+    <t>그래도 부족할 수 있으니 우주선이 돌아오기 전에 상점에서 조금 주문을 해볼까요?</t>
+  </si>
+  <si>
+    <t>상점 데이터 칩에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>데이터 패널 화면에서는 데이터 칩을 눌러서 화면을 전환할 수 있습니다. 상점은 {S}키를 눌러서 전환할 수 있죠.</t>
+  </si>
+  <si>
+    <t>아이템의 종류에 따라 씨앗, 로봇, 부품, 건축 키트 메뉴가 나뉘어져 구성되어 있습니다.</t>
+  </si>
+  <si>
+    <t>아까 이야기한 당근 씨앗부터 구매해보죠.</t>
+  </si>
+  <si>
+    <t>당근 씨앗 구매 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>구매 수량은 +버튼을 누르거나 숫자칸을 클릭해 직접 입력해서 정할 수 있습니다. 우선 50개만 구매해보죠.</t>
+  </si>
+  <si>
+    <t>숫자 칸에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이번에는 축사에서 키울 소랑 우유를 담을 병도 구매를 해봅시다.</t>
+  </si>
+  <si>
+    <t>자동 스크롤 및 소 구매 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>우유같은 축산물은 농작물보다 시장 경제에서 불안정하지만 운이 좋다면 한 번에 큰 돈을 벌 수 있을겁니다.</t>
+  </si>
+  <si>
+    <t>구매 확정 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>그래도 과투자 하는 것은 좋지 않으니 10개만 구매하는걸로 하죠.</t>
+  </si>
+  <si>
+    <t>빈 병 20개 구매 네비게이팅</t>
+  </si>
+  <si>
+    <t>자 이번에는 플레이어님을 대신해서 자동으로 일해 줄 로봇과 우유를 생산하는 소를 구매해봅시다.</t>
+  </si>
+  <si>
+    <t>상점 오브젝트 메뉴 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>지금 당장은 프로토타입 버전 뿐이지만… 앞으로 좋은 결과가 있을거라 생각되네요.</t>
+  </si>
+  <si>
+    <t>프로토타입과 소는 저희가 2개 까지 무료로 드리도록 하겠습니다. 패키지 상품으로 구매해보세요.</t>
+  </si>
+  <si>
+    <t>프로토타입/소 패키지 상품에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>모두 구매를 하니 12시가 되어가는군요. 곧 우주선이 돌아올 시간입니다.</t>
+  </si>
+  <si>
+    <t>구매한 아이템들은 우주선이 복귀할 때 실어서 같이 배송되기 때문에 우주선이 복귀하기 전에 구매를 끝마치는게 중요하죠.</t>
+  </si>
+  <si>
+    <t>만약 우주선이 출발한 이후에 주문을 하면 우주선을 다시 보내야 수령할 수 있는 것이죠.</t>
+  </si>
+  <si>
+    <t>그렇다고 한 번 살 때 너무 많이 구매를 하면 창고가 가득 차 재고를 하차하지 못하고, 심지어는 상품이 사라질 수 있으니 조심하세요.</t>
+  </si>
+  <si>
+    <t>자 이제 우주선이 도착한 것 같네요. 도착한 로봇들에게도 일을 시켜 볼까요?</t>
+  </si>
+  <si>
+    <t>로봇 관리 데이터 칩에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이 화면에서는 보유 중인 모든 자동화 로봇의 정보를 보거나 이름을 바꿔줄 수 있습니다.</t>
+  </si>
+  <si>
+    <t>지금은 모든 로봇이 일을 안하고 있어서 자고 있는 모습이네요.</t>
+  </si>
+  <si>
+    <t>첫 번째 로봇의 이름을 한 번 바꿔볼까요? 원하는 이름 아무거나 지어주세요.</t>
+  </si>
+  <si>
+    <t>첫 번째 로봇에 이름 칸에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>{input}. 좋은 이름이네요. 이제 명령 하달을 위해 프로토타입의 인터페이스로 들어가보죠.</t>
+  </si>
+  <si>
+    <t>첫 번째 로봇 칸에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_NPC_Interface</t>
+  </si>
+  <si>
+    <t>각각의 로봇 인터페이스는 지금처럼 로봇 관리 패널로 들어오거나 필드의 로봇에게 직접 상호작용을 해서 들어올 수 있습니다.</t>
+  </si>
+  <si>
+    <t>화면에 표시된 곳을 누르고 설치했던 밭을 클릭해 보세요.</t>
+  </si>
+  <si>
+    <t>작업 구역 버튼에 반짝이는 효과, 이후에 필드 밭에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>로봇 한 기는 밭 4개까지 담당해서 일을 할 수 있습니다. 물론 다른 로봇들에게도 같은 밭을 담당시킬 수 있지만, 효율적이진 않죠.</t>
+  </si>
+  <si>
+    <t>작업 구역을 할당했으니, 이제는 어떤 것을 생산할지 명령해야겠죠? 당근을 생산하도록 명령하세요.</t>
+  </si>
+  <si>
+    <t>생산 아이템 버튼에 반짝이는 효과, 이후에 나오는 목록에 당근에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이제 로봇이 스스로 일을 하는 모습이 보이죠? 로봇은 움직이거나 일을 할 때 수소 에너지를 소모하여 물을 생산합니다.</t>
+  </si>
+  <si>
+    <t>밭에 물을 주는 식으로 소모를 하긴 하지만 물이 가득 차게 된다면 잠시 작업이 중단되고 제자리에서 물을 뿜어내는 시간이 필요합니다.</t>
+  </si>
+  <si>
+    <t>그리고 사용 중인 배터리의 용량이 부족해지면 스스로 창고에서 충전된 배터리로 교체를 하기도 하죠.</t>
+  </si>
+  <si>
+    <t>프로토타입이긴 해도 최대한 스스로 해결할 수 있도록 만들어졌으니 걱정하지 않으셔도 됩니다.</t>
+  </si>
+  <si>
+    <t>이제 다른 놀고 있는 프로토타입에게도 일을 할당해보죠.</t>
+  </si>
+  <si>
+    <t>두 번째 로봇 오브젝트에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>이번에는 축사에서 일을 시켜 봅시다.</t>
+  </si>
+  <si>
+    <t>축사 건물에 작업 구역 할당 네비게이팅</t>
+  </si>
+  <si>
+    <t>축사에 배치를 한다면 구매했던 소들을 알아서 잘 몰아오게 됩니다. 다행히 소들이 근처에 있네요.</t>
+  </si>
+  <si>
+    <t>축사는 밭과 달리 하나의 축사에서만 작업이 가능한 것도 기억해주세요.</t>
+  </si>
+  <si>
+    <t>데려온 소 들은 귀한 몸이기 때문에 축사 건물에 갇혀 있는 것이 아닌 울타리 내에서 자유롭게 풀을 뜯어 먹고 살겁니다.</t>
+  </si>
+  <si>
+    <t>축사에 배치된 소에게 카메라 이동</t>
+  </si>
+  <si>
+    <t>마실 물은 축사 건물 오른 쪽에 소형 물탱크로 확보할 수 있습니다.</t>
+  </si>
+  <si>
+    <t>카메라 위치 지하수 펌핑 장치로 이동</t>
+  </si>
+  <si>
+    <t>로봇이 물을 뿜어낼 때도 있으니 수분은 크게 신경 안쓰셔도 될겁니다.</t>
+  </si>
+  <si>
+    <t>카메라 위치 두 번째 로봇 위치로 원상복귀</t>
+  </si>
+  <si>
+    <t>소와 같은 가축은 특정 주기마다 고정적으로 상품을 생산합니다.</t>
+  </si>
+  <si>
+    <t>축사에 로봇을 배치하면 자동으로 생산이 되긴 하겠지만, 빈 병을 들고 직접 소에게 상호작용해도 생산할 수 있으니 참고해주세요.</t>
+  </si>
+  <si>
+    <t>마지막으로 로봇의 업그레이드에 관한 것을 알려드리겠습니다.</t>
+  </si>
+  <si>
+    <t>로봇 업그레이드 메뉴 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>현재 프로토타입의 성능은 상당히 좋지 못한 편입니다. 이동속도부터 작업 효율까지 모든 면에서 말이죠.</t>
+  </si>
+  <si>
+    <t>기체 자체를 업그레이드할 수는 없지만, 업그레이드 퍽을 장착하여 성능을 조금 올릴 수 있죠.</t>
+  </si>
+  <si>
+    <t>표시된 영역을 한 번 클릭해서 장착해보세요. 이동 속도가 확 빨라질겁니다.</t>
+  </si>
+  <si>
+    <t>속도 부품 슬롯에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>장착 해제를 하고 싶다면 다시 한 번 클릭해서 해제를 하면 되겠습니다.</t>
+  </si>
+  <si>
+    <t>Tutorial_BIC_Skip</t>
   </si>
   <si>
     <t>이미 잘 아시는 것 같군요. 지금 부터 자유롭게 게임을 즐겨주시면 되겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>그래도 혹시 모르니 튜토리얼이 필요하실 땐 알림 버튼을 눌러서 튜토리얼 진행하기를 선택해주세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basic_BIC</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial_BIC</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그러면 우선 슈트 조작 방법을 설명드리겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>화면에 반짝이는 타일에 우클릭을 해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>플레이어 좌측으로 두 칸 떨어진 위치의 타일에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금처럼 원하는 타일에 우클릭을 하면 그 위치로 이동을 할 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음으로 반짝이는 건물에 좌클릭을 해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>원하는 건물이나 캐릭터에 좌클릭을 하면 상호작용을 할 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>상호작용을 하면 지금처럼 오브젝트의 인터페이스가 등장하며 관련된 작업을 할 수 있죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우선 물탱크에 좌클릭을 해서 물병을 얻어볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>물탱크에 클릭 표시</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>만약 보조 인벤토리가 가득 차 있다면 물탱크를 눌러도 물병을 얻을 수 없으니 조심하세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 전지를 충전해봅시다. 오른 쪽 하단 슬롯에 있는 아이템을 더블 클릭하거나 표시된 영역에 드래그해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전 슬롯 첫 번째 칸에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수소 전지라는 이름 답게 물을 분해해서 얻은 수소를 채워 넣는 방식으로 충전을 시키죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>일일이 단자에 충전시키는 것이 번거롭다면 자동 충전 토글이나 일괄 충전 버튼을 눌러보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전이 끝나면 자동으로 메인 창고로 이동을 하니 과충전으로 인한 사고는 걱정 안하셔도 되겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 이 곳에서의 볼일은 끝났으니 나가볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>EXIT버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제는 일을 시작할 시간입니다. 밭을 먼저 설치해야겠죠?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>건설 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>방금 누르신 버튼은 건축 모드로 들어가는 버튼입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>건축 모드에서는 건물을 제외한 다른 캐릭터 오브젝트는 비활성화 처리가 되고, 타일의 그리드가 강조됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭을 한 번 눌러보시겠어요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>건물 "밭" 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭을 포함한 원하는 건물을 선택하면 왼 쪽에 그 건물의 크기와 보유하고 있는 건물 키트의 개수를 확인할 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭 같은 경우는 단순히 땅을 갈기만 하면 되기 때문에 키트는 필요 없이 무한으로 표시가 되죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자 그러면 표시된 영역에 밭을 설치해 볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭 설치 영역에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>건물 "축사"버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 원하는 위치에 설치를 해보세요. 밭이나 이미 다른 건물이 있는 위치에는 설치하지 못합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>카메라는 캐릭터를 따라가지 않습니다. 커서를 화면 끝으로 이동시키면 그 방향으로 이동하죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘 하셨습니다. 이번에는 소를 키울 축사도 하나 만들어 볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>축사 같이 키트를 소모해야 하는 건물은 설치한 영역에 부지가 먼저 생성이 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금처럼 키트가 있는 경우에는 즉시 설치가 진행이 되지만, 키트가 없다면 구매를 해서 수령할 때 까지 기다려야 하죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 건축 모드를 종료해보죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>건축 모드 종료 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>보조 인벤토리 1번 슬롯에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>먼저 밭에서 일하는 방법을 알려드리겠습니다. {1번} 키를 누르거나 슬롯을 클릭해서 씨감자를 사용할 준비를 해볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 빈 밭에 한 칸 씩 상호작용해서 심어봅시다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>심을 때 마다 한 칸 씩 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>잘 하셨습니다. 감자가 자라는 시간은 하루 정도 걸리긴 하지만… 이번만 빠르게 시간을 돌려볼게요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자, 다 자란 감자들을 하나 씩 클릭해서 수확해보죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>모든 감자를 바로 성장시키기</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수확할 때 마다 한 칸 씩 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수확한 아이템들은 모두 가운데에 있는 슬롯에 저장됩니다. 메인 인벤토리라고 부르죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 창고 건물에 상호작용을 해볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 창고 건물에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템을 모두 저장하거나 꺼낼 때는 방금 처럼 하시면 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>꺼낼 아이템에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수확한 감자를 더블 클릭하거나 창고에 드래그해서 저장해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>감자 아이템에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>적재 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 낱개로 꺼내볼까요? Ctrl키를 누른 채로 당근 씨앗을 좌클릭해서 꺼내보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 수확한 감자를 팔아봅시다. 적재 버튼을 눌러보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>적재 모드에서는 창고와의 상호작용이 모두 우주선에서 이루어진다 생각하시면 되겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그러면 감자를 더블 클릭하거나 우주선 슬롯에 드래그해서 적재를 해봅시다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>창고에 있는 감자에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우주선에 적재를 하면 현재 가격에 따른 정산 금액이 표시됩니다. 오늘은 감자 가격이 조금 오른 편이군요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>정산 금액 Panel에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 우주선 출발 준비를 시켜볼까요? 적재 완료 버튼을 눌러보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>적재 완료 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우주선은 다음 날 자정에 출발을 합니다. 그래서 전날 23시부터는 출발을 위해 적재 버튼이 비활성화 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우선 빠른 판매를 위해 시간을 조금 돌려 볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>다음 날 오전 8시로 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그런데 오전 9시가 되면 아이템들의 가격이 변하기 때문에 가격 변동 추이도 확인을 해봐야 하겠습니다. 마침 오늘은 월요일이기도 하네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 데이터 패널 버튼을 눌러보세요. {C}키를 누르셔도 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터 패널 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>앞으로 플레이어님이 많이 보게 되실 데이터 패널 화면입니다. 판매할 수 있는 아이템들의 가격이 어떻게 변했는지 볼 수 있죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>저희가 팔았던 감자의 가격 변동을 한 번 볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>감자 아이템 정보 Panel에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 화면에서는 일 주일 간의 가격 변동 추이를 차트로 볼 수 있는 화면입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오늘의 감자 값은 떨어졌네요. 어제 올랐을 때 팔아서 정말 다행입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그리고 오늘은 월요일이기 때문에 아이템들에 대한 뉴스가 나오는 날입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴스에 따라 아이템 가격이 크게 오르거나 떨어지기 때문에 꼭 확인을 하는 것이 중요하죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>뉴스 인덱스 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그에 비해 당근은 가격이 오르는 호재가 나온 상황입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>마침 창고에 당근 씨앗을 준비해뒀었는데, 오히려 잘 되었네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그래도 부족할 수 있으니 우주선이 돌아오기 전에 상점에서 조금 주문을 해볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>상점 데이터 칩에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>데이터 패널 화면에서는 데이터 칩을 눌러서 화면을 전환할 수 있습니다. 상점 같은 경우는 S를 눌러도 되죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템의 종류에 따라 씨앗, 로봇, 부품, 건축 키트 메뉴가 나뉘어져 구성되어 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우선 당근 씨앗부터 구매를 해볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근 씨앗 구매 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구매 수량은 +버튼을 누르거나 숫자칸을 클릭해 직접 입력해서 정할 수 있습니다. 우선 50개만 구매 해볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>숫자 칸에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇 메뉴 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 축사에서 키울 소랑 우유를 담을 병도 구매를 해봅시다. 우선 소 부터 한 마리 구매해보죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자동 스크롤 및 소 구매 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>소는 지구를 떠난 이후부터 상당히 비싼 몸값이 되었죠. 그래도 첫 정착인 만큼 한 마리는 무상 지원을 해드리기로 했습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구매 확정 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>대신 빈 병은 직접 구매해주세요. 넉넉하게 20개만 구매해보죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>빈 병 20개 구매 네비게이팅</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자 이번에는 플레이어님을 대신해서 자동으로 일해 줄 로봇을 구매해봅시다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금 당장은 프로토타입 버전 뿐이지만… 앞으로 좋은 결과가 있을거라 생각되네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로토타입 구매 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로토타입도 소와 마찬가지로 초기 정착 지원 형태로 두 기를 무상 지원해드리겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로토타입 두 기 구매 네비게이팅</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>구매한 아이템들은 우주선이 복귀할 때 실어서 같이 배송되기 때문에 우주선이 복귀하기 전에 구매를 끝마치는게 중요하죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>모두 구매를 하니 12시가 되어가는군요. 곧 우주선이 출발할 시간입니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>만약 우주선이 출발한 이후에 주문을 하면 우주선을 다시 보내야 수령할 수 있는 것이죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그렇다고 한 번 살 때 너무 많이 구매를 하면 우주선에 모두 실을 수 없기 때문에 이 부분도 조심 하셔야겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>자 이제 우주선이 도착한 것 같네요. 도착한 로봇들에게도 일을 시켜 볼까요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇 관리 데이터 칩에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금은 모든 로봇이 일을 안하고 있어서 자고 있는 모습이네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이 화면에서는 보유 중인 모든 자동화 로봇의 정보를 보거나 이름을 바꿔줄 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>첫 번째 로봇에 이름 칸에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>첫 번째 로봇의 이름을 한 번 바꿔볼까요? 원하는 이름 아무거나 지어주세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>{input}. 좋은 이름이네요. 이제 명령 하달을 위해 프로토타입의 인터페이스로 들어가보죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>첫 번째 로봇 칸에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>각각의 로봇 인터페이스는 지금처럼 로봇 관리 패널로 들어오거나 필드의 로봇에게 직접 상호작용을 해서 들어올 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>화면에 표시된 곳을 누르고 설치했던 밭을 클릭해 보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업 구역 버튼에 반짝이는 효과, 이후에 필드 밭에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇 한 기는 밭 4개까지 담당해서 일을 할 수 있습니다. 물론 다른 로봇들에게도 같은 밭을 담당시킬 수 있지만, 효율적이진 않죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업 구역을 할당했으니, 이제는 어떤 것을 생산할지 명령해야겠죠? 이번에는 당근을 심도록 해봅시다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>생산 아이템 버튼에 반짝이는 효과, 이후 목록에 당근에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 로봇이 스스로 일을 하는 모습이 보이죠? 로봇은 움직이거나 일을 할 때 수소 에너지를 소모하여 물을 생산합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그리고 사용 중인 배터리의 용량이 부족해지면 스스로 창고에서 충전된 배터리로 교체를 하기도 하죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로토타입이긴 해도 최대한 스스로 해결할 수 있도록 만들어졌으니 걱정하지 않으셔도 됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이제 다른 놀고 있는 프로토타입에게도 일을 할당해보죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>두 번째 로봇 오브젝트에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이번에는 축사에서 일을 시켜 봅시다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>축사 건물에 작업 구역 할당 네비게이팅</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>축사에 배치를 한다면 구매했던 소들을 알아서 잘 몰아오게 됩니다. 다행히 소들이 근처에 있네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>데려온 소 들은 귀한 몸이기 때문에 축사 건물에 갖혀 있는 것이 아닌 울타리 내에서 자유롭게 풀을 뜯어 먹고 살겁니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>마실 물은 축사 건물 오른 쪽에 지하수 펌핑 장치로 확보할 수 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>카메라 위치 지하수 펌핑 장치로 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>카메라 위치 두 번째 로봇 위치로 원상복귀</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>축사는 밭과 달리 하나의 축사에서만 작업이 가능한 것도 기억해주세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>축사에 배치된 소에게 카메라 이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>정 부족한 물은 로봇이 생산하는 수분으로도 충분히 해결할 수 있습니다. 덕분에 축사에서 일하는 로봇은 물을 분출할 일이 없죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>마지막으로 로봇의 업그레이드에 관한 것을 알려드리겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇 업그레이드 메뉴 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>현재 프로토타입의 성능은 상당히 좋지 못한 편입니다. 이동속도부터 작업 효율까지 모든 면에서 말이죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>기체 자체를 업그레이드할 수는 없지만, 업그레이드 퍽을 장착하여 성능을 조금 올릴 수 있죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>제가 미리 적재해둔 속도 업그레이드 부품이 아이템 슬롯에 보이죠? 더블 클릭을 하거나 맞는 위치에 드래그해서 장착해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>속도 부품에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>확실히 로봇의 이동 속도가 빨라졌네요. 아직 연구 중인 로봇이기 때문에 성능에 한계는 있지만… 열심히 개발해보겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>알림 버튼에 반짝이는 효과</t>
+  </si>
+  <si>
+    <t>Tutorial_Basic_End</t>
   </si>
   <si>
     <t>여기까지 튜토리얼을 마치도록 하겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>알림 버튼에 반짝이는 효과</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>남은 목표는 더 많은 프로토타입을 이용한 자동화 농장을 운영하며 매일 가격이 변화하는 시장에서 1억을 목표로 달려봅시다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial_Basic_End</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial_BIC_Skip</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial_BIC_Manual</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tutorial_BIC_HDR</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>오늘 감자 가격이 조금 떨어진 이유가 악재 때문이었네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>우주선이 출발했고, 08시가 되면 정산된 금액이 입금됩니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>어제는 평소보다 가격이 조금 올랐는데, 곧 09시니 가격이 어떻게 변할지 궁금하긴 하네요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>물병은 사용할 수 있는 아이템이기 때문에 왼 쪽에 3칸짜리 인벤토리에 생성됩니다. 보조 인벤토리라고 부르죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>지금 화면은 하이드로 리엑터라고 하는 건물의 인터페이스입니다. 수소 전지를 충전하거나 물을 얻을 수 있는 인터페이스죠.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Turotial_BIC</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>루크</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>수확을 하고 나면 밭에 수분이 조금 떨어집니다. 밭에 한 번 커서를 올려보시겠어요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭에 커서 표시</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>부족한 수분은 방금 얻은 물병의 물을 사용해서 채울 수 있습니다. 이번엔 물병을 밭에 사용해보세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭에 수분이 부족하면 작물을 심을 수 없으니 직접 작물을 기를 때는 수분량을 조심해야 합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>밭에 물을 주는 식으로 소모를 하긴 하지만 물이 가득 차게 된다면 잠시 작업이 중단되고 제자리에서 물을 뿜어내는 시간이 필요합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionType</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsRebindable</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mouse0</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC_Interaction</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mouse1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC_Movement</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUp_Chart</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>S</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUp_Shop</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>R</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUp_Robot</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>E</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUp_Storage</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>H</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUp_Hydro</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Select_Slot1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Select_Slot2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Select_Slot3</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prototype</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cow</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chicken</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Object</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>KeyID</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>DefaultKeyCode</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Movement</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Interaction</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Selection</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description_KR</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>상호작용</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>차트</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>상점</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>로봇 관리</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>창고</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>하이드로 리엑터</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1번 슬롯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2번 슬롯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>3번 슬롯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionName</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Modifier1</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Modifier2</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopUp_Setting</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Escape</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>설정</t>
+  </si>
+  <si>
+    <t>Tutorial</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>100000G</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ObjectPackage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Developer</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Field</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1484,11 +1317,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="0.0_ "/>
-    <numFmt numFmtId="177" formatCode="0_ "/>
-  </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1655,8 +1484,20 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1842,8 +1683,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E8E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1955,6 +1802,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2106,17 +1968,17 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2592,7 +2454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
@@ -2646,7 +2508,7 @@
         <v>800</v>
       </c>
       <c r="E2" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F2" s="2">
         <v>-1</v>
@@ -2669,7 +2531,7 @@
         <v>1000</v>
       </c>
       <c r="E3" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2">
         <v>30</v>
@@ -2693,7 +2555,7 @@
         <v>720</v>
       </c>
       <c r="E4" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2">
         <v>-1</v>
@@ -2716,7 +2578,7 @@
         <v>900</v>
       </c>
       <c r="E5" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -2740,7 +2602,7 @@
         <v>800</v>
       </c>
       <c r="E6" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F6" s="2">
         <v>-1</v>
@@ -2763,7 +2625,7 @@
         <v>1000</v>
       </c>
       <c r="E7" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2">
         <v>20</v>
@@ -2787,7 +2649,7 @@
         <v>880</v>
       </c>
       <c r="E8" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F8" s="2">
         <v>-1</v>
@@ -2810,7 +2672,7 @@
         <v>1100</v>
       </c>
       <c r="E9" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -2834,7 +2696,7 @@
         <v>960</v>
       </c>
       <c r="E10" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F10" s="2">
         <v>-1</v>
@@ -2857,7 +2719,7 @@
         <v>1200</v>
       </c>
       <c r="E11" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2">
         <v>15</v>
@@ -2881,7 +2743,7 @@
         <v>880</v>
       </c>
       <c r="E12" s="2">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2">
         <v>-1</v>
@@ -2904,7 +2766,7 @@
         <v>1100</v>
       </c>
       <c r="E13" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>15</v>
@@ -2974,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="F16" s="2">
         <v>-1</v>
@@ -2985,16 +2847,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>6021</v>
+        <v>5011</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="D17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
@@ -3008,16 +2870,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>6031</v>
+        <v>5021</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="D18" s="2">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
@@ -3031,16 +2893,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>6032</v>
+        <v>6021</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>330</v>
+        <v>155</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>331</v>
+        <v>158</v>
       </c>
       <c r="D19" s="2">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
@@ -3049,21 +2911,21 @@
         <v>-1</v>
       </c>
       <c r="G19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>7011</v>
+        <v>6031</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="D20" s="2">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -3077,16 +2939,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>8011</v>
+        <v>6032</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="D21" s="2">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E21" s="2">
         <v>1</v>
@@ -3095,21 +2957,21 @@
         <v>-1</v>
       </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>8012</v>
+        <v>7011</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="D22" s="2">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="2">
         <v>1</v>
@@ -3118,15 +2980,15 @@
         <v>-1</v>
       </c>
       <c r="G22" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>8021</v>
+        <v>8011</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>56</v>
@@ -3146,10 +3008,10 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>8022</v>
+        <v>8012</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>56</v>
@@ -3169,10 +3031,10 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>8031</v>
+        <v>8021</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>56</v>
@@ -3192,10 +3054,10 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>8032</v>
+        <v>8022</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>56</v>
@@ -3215,10 +3077,10 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>8041</v>
+        <v>8031</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>56</v>
@@ -3238,10 +3100,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8042</v>
+        <v>8032</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>56</v>
@@ -3261,16 +3123,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>9011</v>
+        <v>8041</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D29" s="2">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="E29" s="2">
         <v>1</v>
@@ -3284,16 +3146,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>9021</v>
+        <v>8042</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D30" s="2">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
@@ -3302,12 +3164,81 @@
         <v>-1</v>
       </c>
       <c r="G30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>9001</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>9011</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G33" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G30">
-    <sortCondition ref="A2:A30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G33">
+    <sortCondition ref="A2:A33"/>
   </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
@@ -3344,1741 +3275,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10ECB86C-D64A-46E1-8165-2F7D3A7C7284}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A3">TRANSPOSE(ConfigurationDataTable!A1:B1)</f>
-        <v>GameDayDuration</v>
-      </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>TutorialEnabled</v>
-      </c>
-      <c r="B3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
-  <dimension ref="A1:F108"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="22.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="65.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>100001</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>100002</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>100003</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>110001</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>110002</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>110003</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>110004</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>110005</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>110006</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>110007</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>110008</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>110009</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>110010</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>110011</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>110012</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>110013</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>110014</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>110015</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
-        <v>110016</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>110017</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
-        <v>110018</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
-        <v>110019</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>110020</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>110021</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
-        <v>110022</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>110023</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>110024</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>110025</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
-        <v>110026</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
-        <v>110027</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>110028</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>110029</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>110030</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
-        <v>110031</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>110032</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
-        <v>110033</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
-        <v>110034</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
-        <v>110035</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
-        <v>110036</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
-        <v>110037</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
-        <v>110038</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
-        <v>110039</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
-        <v>110040</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
-        <v>110041</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
-        <v>110042</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
-        <v>110043</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
-        <v>110044</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
-        <v>110045</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
-        <v>110046</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
-        <v>110047</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
-        <v>110048</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
-        <v>110049</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
-        <v>110050</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="2">
-        <v>110051</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="2">
-        <v>110052</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
-        <v>110053</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
-        <v>110054</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="2">
-        <v>110055</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="2">
-        <v>110056</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="2">
-        <v>110057</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
-        <v>110058</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="2">
-        <v>110059</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="2">
-        <v>110060</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="2">
-        <v>110061</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="2">
-        <v>110062</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="2">
-        <v>110063</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="2">
-        <v>110064</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="2">
-        <v>110065</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="2">
-        <v>110066</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="2">
-        <v>110067</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>110068</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>110069</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
-        <v>110070</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
-        <v>110071</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
-        <v>110072</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
-        <v>110073</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
-        <v>110074</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
-        <v>110075</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
-        <v>110076</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="2">
-        <v>110077</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="2">
-        <v>110078</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
-        <v>110079</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="2">
-        <v>110080</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
-        <v>110081</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
-        <v>110082</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
-        <v>110083</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
-        <v>110084</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
-        <v>110085</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
-        <v>110086</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
-        <v>110087</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
-        <v>110088</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
-        <v>110089</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
-        <v>110090</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="2">
-        <v>110091</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="2">
-        <v>110092</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="2">
-        <v>110093</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="2">
-        <v>110094</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
-        <v>110095</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="2">
-        <v>110096</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="2">
-        <v>110097</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="2">
-        <v>110098</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="2">
-        <v>110099</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="2">
-        <v>110100</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="2">
-        <v>190001</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
-        <v>190002</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="2">
-        <v>190101</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="2">
-        <v>190102</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F140">
-    <sortCondition ref="A2:A140"/>
-  </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
   <dimension ref="A1:C7"/>
@@ -5193,28 +3389,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>176</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>136</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>333</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>350</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>351</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>310</v>
+        <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>338</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -5222,25 +3418,25 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>314</v>
+        <v>141</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>336</v>
+        <v>163</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>311</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>340</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5248,25 +3444,25 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>312</v>
+        <v>139</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>334</v>
+        <v>161</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>313</v>
+        <v>140</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>339</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -5274,25 +3470,25 @@
         <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>316</v>
+        <v>143</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>315</v>
+        <v>142</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>341</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -5300,25 +3496,25 @@
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>318</v>
+        <v>145</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>317</v>
+        <v>144</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>342</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -5326,25 +3522,25 @@
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>320</v>
+        <v>147</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>319</v>
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>343</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -5352,25 +3548,25 @@
         <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>322</v>
+        <v>149</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>321</v>
+        <v>148</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>344</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -5378,25 +3574,25 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>324</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>323</v>
+        <v>150</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>345</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -5404,25 +3600,25 @@
         <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>353</v>
+        <v>180</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>354</v>
+        <v>181</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>355</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -5430,25 +3626,25 @@
         <v>41</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>325</v>
+        <v>152</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>337</v>
+        <v>164</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G10" s="2">
         <v>1</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>346</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -5456,25 +3652,25 @@
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>337</v>
+        <v>164</v>
       </c>
       <c r="D11" s="2">
         <v>2</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>347</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -5482,25 +3678,25 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>327</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>337</v>
+        <v>164</v>
       </c>
       <c r="D12" s="2">
         <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>352</v>
+        <v>179</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>348</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -5923,7 +4119,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
@@ -6271,23 +4467,6 @@
       </c>
       <c r="E20" s="2" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>990</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -6330,16 +4509,16 @@
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>54</v>
@@ -6351,10 +4530,10 @@
         <v>48</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>111</v>
@@ -6368,7 +4547,7 @@
         <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -6400,16 +4579,16 @@
         <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D3" s="3">
         <v>10000</v>
       </c>
       <c r="E3" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3">
         <v>4</v>
@@ -6429,10 +4608,10 @@
         <v>6031</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D4" s="3">
         <v>20000</v>
@@ -6461,10 +4640,10 @@
         <v>6032</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D5" s="3">
         <v>5000</v>
@@ -6526,7 +4705,7 @@
         <v>ObjectID</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>80</v>
@@ -6537,7 +4716,7 @@
         <v>ObjectName</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
         <v>81</v>
@@ -6548,7 +4727,7 @@
         <v>ObjectType</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
         <v>109</v>
@@ -6559,7 +4738,7 @@
         <v>Price</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
         <v>80</v>
@@ -6570,7 +4749,7 @@
         <v>MainInv</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
         <v>80</v>
@@ -6581,7 +4760,7 @@
         <v>SubInv</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
         <v>80</v>
@@ -6592,7 +4771,7 @@
         <v>Speed</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>101</v>
@@ -6603,7 +4782,7 @@
         <v>WorkDuration</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>101</v>
@@ -6614,7 +4793,7 @@
         <v>ProductionAmount</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
         <v>80</v>
@@ -6625,7 +4804,7 @@
         <v>UseToDemo</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>80</v>
@@ -6638,34 +4817,1865 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E772BBA4-8366-43B3-9824-1E271127840B}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="25.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
-        <v>900</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0</v>
-      </c>
+        <v>100001</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>100002</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>100003</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>110001</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>110002</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>110003</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>110004</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>110005</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>110006</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>110007</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>110008</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>110009</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>110010</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>110011</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>110012</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>110013</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>110014</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>110015</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>110016</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>110017</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>110018</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>110019</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>110020</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>110021</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>110022</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>110023</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>110024</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>110025</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>110026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>110027</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>110028</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>110029</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>110030</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>110031</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>110032</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>110033</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>110034</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>110035</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>110036</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+    </row>
+    <row r="41" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>110037</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>110038</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>110039</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+    </row>
+    <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>110040</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>110041</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+    </row>
+    <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>110042</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>110043</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>110044</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>110045</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+    </row>
+    <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>110046</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>110047</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+    </row>
+    <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>110048</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>110049</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>110050</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+    </row>
+    <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>110051</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>110052</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+    </row>
+    <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>110053</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+    </row>
+    <row r="58" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>110054</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+    </row>
+    <row r="59" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>110055</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>110056</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E60" s="8"/>
+      <c r="F60" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>110057</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>110058</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>110059</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>110060</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>110061</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+    </row>
+    <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>110062</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+    </row>
+    <row r="67" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>110063</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>110064</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>110065</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>110066</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
+        <v>110067</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>110068</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7">
+        <v>110069</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+    </row>
+    <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
+        <v>110070</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7">
+        <v>110071</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+    </row>
+    <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
+        <v>110072</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+    </row>
+    <row r="77" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
+        <v>110073</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7">
+        <v>110074</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+    </row>
+    <row r="79" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
+        <v>110075</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" s="8"/>
+      <c r="F79" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>110076</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+    </row>
+    <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7">
+        <v>110077</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="82" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7">
+        <v>110078</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>110079</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E83" s="8"/>
+      <c r="F83" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>110080</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+    </row>
+    <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>110081</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E85" s="8"/>
+      <c r="F85" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7">
+        <v>110082</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+    </row>
+    <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>110083</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E87" s="8"/>
+      <c r="F87" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="7">
+        <v>110084</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+    </row>
+    <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="7">
+        <v>110085</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+    </row>
+    <row r="90" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7">
+        <v>110086</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+    </row>
+    <row r="91" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="7">
+        <v>110087</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+    </row>
+    <row r="92" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="7">
+        <v>110088</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="7">
+        <v>110089</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E93" s="8"/>
+      <c r="F93" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="7">
+        <v>110090</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+    </row>
+    <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="7">
+        <v>110091</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+    </row>
+    <row r="96" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="7">
+        <v>110092</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E96" s="8"/>
+      <c r="F96" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="7">
+        <v>110093</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E97" s="8"/>
+      <c r="F97" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7">
+        <v>110094</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E98" s="8"/>
+      <c r="F98" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="7">
+        <v>110095</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+    </row>
+    <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7">
+        <v>110096</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="7">
+        <v>110097</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E101" s="8"/>
+      <c r="F101" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="7">
+        <v>110098</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+    </row>
+    <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="7">
+        <v>110099</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+    </row>
+    <row r="104" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="7">
+        <v>110100</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E104" s="8"/>
+      <c r="F104" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="7">
+        <v>110101</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+    </row>
+    <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="7">
+        <v>190001</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+    </row>
+    <row r="107" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="7">
+        <v>190002</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E107" s="8"/>
+      <c r="F107" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="7">
+        <v>190101</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+    </row>
+    <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="7">
+        <v>190102</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F141">
+    <sortCondition ref="A2:A141"/>
+  </sortState>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA2A848-99C5-4DBB-99DE-0AABE9603FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4939C27-5D71-4E43-9423-3AFA82FC0C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="3" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
     <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
     <sheet name="KeycodeDataTable" sheetId="13" r:id="rId3"/>
     <sheet name="ProductDataTable" sheetId="3" r:id="rId4"/>
-    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId5"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId6"/>
-    <sheet name="ObjectDataTable" sheetId="5" r:id="rId7"/>
-    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId8"/>
-    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId9"/>
+    <sheet name="Calculator" sheetId="14" r:id="rId5"/>
+    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId6"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId7"/>
+    <sheet name="ObjectDataTable" sheetId="5" r:id="rId8"/>
+    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId9"/>
+    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="364">
   <si>
     <t>ItemID</t>
   </si>
@@ -1310,6 +1311,35 @@
   </si>
   <si>
     <t>Field</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 가격</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>표준편차</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>평균회귀 기준 하한가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 ID</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨앗 가격</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템명</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 ID 값을 입력하여 계산
+ID값은 2로 끝나는 작물 아이템이어야 한다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1497,7 +1527,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1686,6 +1716,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8E8E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1949,7 +2003,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1978,6 +2032,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2504,11 +2573,11 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <f>D3*80/100</f>
-        <v>800</v>
+        <f>D3*90/100</f>
+        <v>900</v>
       </c>
       <c r="E2" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F2" s="2">
         <v>-1</v>
@@ -2531,7 +2600,7 @@
         <v>1000</v>
       </c>
       <c r="E3" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
         <v>30</v>
@@ -2551,11 +2620,10 @@
         <v>13</v>
       </c>
       <c r="D4" s="2">
-        <f>D5*80/100</f>
-        <v>720</v>
+        <v>800</v>
       </c>
       <c r="E4" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F4" s="2">
         <v>-1</v>
@@ -2578,7 +2646,7 @@
         <v>900</v>
       </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2">
         <v>30</v>
@@ -2598,11 +2666,11 @@
         <v>13</v>
       </c>
       <c r="D6" s="2">
-        <f>D7*80/100</f>
-        <v>800</v>
+        <f>D7*90/100</f>
+        <v>900</v>
       </c>
       <c r="E6" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2">
         <v>-1</v>
@@ -2625,7 +2693,7 @@
         <v>1000</v>
       </c>
       <c r="E7" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="2">
         <v>20</v>
@@ -2645,11 +2713,11 @@
         <v>13</v>
       </c>
       <c r="D8" s="2">
-        <f>D9*80/100</f>
-        <v>880</v>
+        <f>D9*90/100</f>
+        <v>990</v>
       </c>
       <c r="E8" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F8" s="2">
         <v>-1</v>
@@ -2672,7 +2740,7 @@
         <v>1100</v>
       </c>
       <c r="E9" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" s="2">
         <v>20</v>
@@ -2692,11 +2760,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="2">
-        <f>D11*80/100</f>
-        <v>960</v>
+        <v>1100</v>
       </c>
       <c r="E10" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2">
         <v>-1</v>
@@ -2719,7 +2786,7 @@
         <v>1200</v>
       </c>
       <c r="E11" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2">
         <v>15</v>
@@ -2739,11 +2806,11 @@
         <v>13</v>
       </c>
       <c r="D12" s="2">
-        <f>D13*80/100</f>
-        <v>880</v>
+        <f>D13*90/100</f>
+        <v>990</v>
       </c>
       <c r="E12" s="2">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="F12" s="2">
         <v>-1</v>
@@ -2766,7 +2833,7 @@
         <v>1100</v>
       </c>
       <c r="E13" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="2">
         <v>15</v>
@@ -2786,11 +2853,10 @@
         <v>16</v>
       </c>
       <c r="D14" s="2">
-        <f>D15*80/100</f>
-        <v>1600</v>
+        <v>5000</v>
       </c>
       <c r="E14" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2">
         <v>-1</v>
@@ -2810,13 +2876,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="2">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E15" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F15" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" s="2">
         <v>1</v>
@@ -3201,7 +3267,7 @@
         <v>52</v>
       </c>
       <c r="D32" s="2">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
@@ -3224,7 +3290,7 @@
         <v>52</v>
       </c>
       <c r="D33" s="2">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
@@ -3275,6 +3341,1870 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
+  <dimension ref="A1:F109"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="25.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>100001</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>100002</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>100003</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>110001</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>110002</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>110003</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>110004</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>110005</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>110006</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>110007</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>110008</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>110009</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>110010</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>110011</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>110012</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>110013</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>110014</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>110015</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>110016</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>110017</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>110018</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>110019</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>110020</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>110021</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>110022</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>110023</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>110024</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>110025</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>110026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>110027</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>110028</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>110029</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>110030</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>110031</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>110032</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>110033</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+    </row>
+    <row r="38" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="7">
+        <v>110034</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="7">
+        <v>110035</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="7">
+        <v>110036</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+    </row>
+    <row r="41" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>110037</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>110038</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>110039</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+    </row>
+    <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>110040</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>110041</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="8"/>
+    </row>
+    <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>110042</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="7">
+        <v>110043</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>110044</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>110045</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
+    </row>
+    <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>110046</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>110047</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+    </row>
+    <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>110048</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>110049</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>110050</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+    </row>
+    <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>110051</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>110052</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+    </row>
+    <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>110053</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+    </row>
+    <row r="58" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>110054</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+    </row>
+    <row r="59" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>110055</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>110056</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E60" s="8"/>
+      <c r="F60" s="7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>110057</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+    </row>
+    <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>110058</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>110059</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>110060</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>110061</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+    </row>
+    <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>110062</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+    </row>
+    <row r="67" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>110063</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>110064</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>110065</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>110066</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
+        <v>110067</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>110068</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7">
+        <v>110069</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+    </row>
+    <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
+        <v>110070</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7">
+        <v>110071</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+    </row>
+    <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
+        <v>110072</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+    </row>
+    <row r="77" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
+        <v>110073</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7">
+        <v>110074</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+    </row>
+    <row r="79" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
+        <v>110075</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" s="8"/>
+      <c r="F79" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>110076</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+    </row>
+    <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7">
+        <v>110077</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="82" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7">
+        <v>110078</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>110079</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E83" s="8"/>
+      <c r="F83" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>110080</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+    </row>
+    <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>110081</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E85" s="8"/>
+      <c r="F85" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7">
+        <v>110082</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+    </row>
+    <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>110083</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E87" s="8"/>
+      <c r="F87" s="9" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="7">
+        <v>110084</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+    </row>
+    <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="7">
+        <v>110085</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+    </row>
+    <row r="90" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7">
+        <v>110086</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+    </row>
+    <row r="91" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="7">
+        <v>110087</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+    </row>
+    <row r="92" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="7">
+        <v>110088</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="7">
+        <v>110089</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E93" s="8"/>
+      <c r="F93" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="7">
+        <v>110090</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+    </row>
+    <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="7">
+        <v>110091</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+    </row>
+    <row r="96" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="7">
+        <v>110092</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E96" s="8"/>
+      <c r="F96" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="7">
+        <v>110093</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E97" s="8"/>
+      <c r="F97" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7">
+        <v>110094</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E98" s="8"/>
+      <c r="F98" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="7">
+        <v>110095</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+    </row>
+    <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7">
+        <v>110096</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="7">
+        <v>110097</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E101" s="8"/>
+      <c r="F101" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="7">
+        <v>110098</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+    </row>
+    <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="7">
+        <v>110099</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+    </row>
+    <row r="104" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="7">
+        <v>110100</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E104" s="8"/>
+      <c r="F104" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="7">
+        <v>110101</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+    </row>
+    <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="7">
+        <v>190001</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+    </row>
+    <row r="107" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="7">
+        <v>190002</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E107" s="8"/>
+      <c r="F107" s="7" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="7">
+        <v>190101</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E108" s="8"/>
+      <c r="F108" s="8"/>
+    </row>
+    <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="7">
+        <v>190102</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F141">
+    <sortCondition ref="A2:A141"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
   <dimension ref="A1:C7"/>
@@ -3806,7 +5736,7 @@
         <v>900</v>
       </c>
       <c r="F3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="2">
         <v>1</v>
@@ -3870,7 +5800,7 @@
         <v>1100</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -3934,7 +5864,7 @@
         <v>1100</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -3959,11 +5889,11 @@
         <v>Product</v>
       </c>
       <c r="D8" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="2">
         <f>VLOOKUP(A8, ItemDataTable!A:D,4, FALSE)</f>
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="2">
         <v>1</v>
@@ -3991,6 +5921,106 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67515829-0AFB-4F47-8C6E-31EBDF1B0551}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="10.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>VLOOKUP(A4, ItemDataTable!A:B, 2, FALSE)</f>
+        <v>Milk</v>
+      </c>
+      <c r="C4" s="2">
+        <f>VLOOKUP(A4-1, ItemDataTable!A:D, 4, FALSE)</f>
+        <v>5000</v>
+      </c>
+      <c r="D4" s="2">
+        <f>VLOOKUP(A4, ProductDataTable!A:E,5, FALSE)</f>
+        <v>5000</v>
+      </c>
+      <c r="E4" s="2">
+        <f>VLOOKUP(A4, ProductDataTable!A:E,4, FALSE)</f>
+        <v>0.2</v>
+      </c>
+      <c r="F4" s="11">
+        <f>D4*(1-(E4*2))</f>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="2">
+        <f>1000/100*90</f>
+        <v>900</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="12">
+        <f>D6*(1-(E6*2))</f>
+        <v>880</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F2"/>
+  </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4117,19 +6147,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9" style="2"/>
     <col min="5" max="5" width="106.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -4145,8 +6176,11 @@
       <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -4162,8 +6196,11 @@
       <c r="E2" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>102</v>
       </c>
@@ -4179,8 +6216,11 @@
       <c r="E3" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>103</v>
       </c>
@@ -4196,8 +6236,11 @@
       <c r="E4" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>104</v>
       </c>
@@ -4213,8 +6256,11 @@
       <c r="E5" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>105</v>
       </c>
@@ -4230,8 +6276,11 @@
       <c r="E6" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>106</v>
       </c>
@@ -4247,8 +6296,11 @@
       <c r="E7" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>201</v>
       </c>
@@ -4264,8 +6316,11 @@
       <c r="E8" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>202</v>
       </c>
@@ -4281,8 +6336,11 @@
       <c r="E9" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>203</v>
       </c>
@@ -4298,8 +6356,11 @@
       <c r="E10" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>211</v>
       </c>
@@ -4315,8 +6376,11 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>212</v>
       </c>
@@ -4332,8 +6396,11 @@
       <c r="E12" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>213</v>
       </c>
@@ -4349,8 +6416,11 @@
       <c r="E13" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>214</v>
       </c>
@@ -4366,8 +6436,11 @@
       <c r="E14" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>301</v>
       </c>
@@ -4383,8 +6456,11 @@
       <c r="E15" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>302</v>
       </c>
@@ -4400,8 +6476,11 @@
       <c r="E16" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>303</v>
       </c>
@@ -4417,8 +6496,11 @@
       <c r="E17" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>304</v>
       </c>
@@ -4434,8 +6516,11 @@
       <c r="E18" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>311</v>
       </c>
@@ -4451,8 +6536,11 @@
       <c r="E19" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>312</v>
       </c>
@@ -4467,6 +6555,9 @@
       </c>
       <c r="E20" s="2" t="s">
         <v>99</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4490,7 +6581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4679,7 +6770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4814,1868 +6905,4 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="25.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="74.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>100001</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>100002</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>100003</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>110001</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>110002</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>110003</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>110004</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>110005</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>110006</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>110007</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>110008</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>110009</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>110010</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>110011</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>110012</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>110013</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>110014</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>110015</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>110016</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>110017</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>110018</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>110019</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>110020</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>110021</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>110022</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>110023</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>110024</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>110025</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>110026</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>110027</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>110028</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>110029</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>110030</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>110031</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>110032</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>110033</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>110034</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
-        <v>110035</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>110036</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>110037</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>110038</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
-        <v>110039</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
-        <v>110040</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
-        <v>110041</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
-        <v>110042</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
-        <v>110043</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
-        <v>110044</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
-        <v>110045</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
-        <v>110046</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
-        <v>110047</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
-        <v>110048</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
-        <v>110049</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
-        <v>110050</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-    </row>
-    <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
-        <v>110051</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
-        <v>110052</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-    </row>
-    <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
-        <v>110053</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-    </row>
-    <row r="58" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
-        <v>110054</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-    </row>
-    <row r="59" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
-        <v>110055</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="60" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
-        <v>110056</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
-        <v>110057</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
-        <v>110058</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
-        <v>110059</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
-        <v>110060</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
-        <v>110061</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="7">
-        <v>110062</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="67" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
-        <v>110063</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="E67" s="8"/>
-      <c r="F67" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="7">
-        <v>110064</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
-        <v>110065</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="7">
-        <v>110066</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="7">
-        <v>110067</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="E71" s="8"/>
-      <c r="F71" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7">
-        <v>110068</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="7">
-        <v>110069</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-    </row>
-    <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7">
-        <v>110070</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E74" s="8"/>
-      <c r="F74" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="7">
-        <v>110071</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="7">
-        <v>110072</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-    </row>
-    <row r="77" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="7">
-        <v>110073</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-    </row>
-    <row r="78" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="7">
-        <v>110074</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="79" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
-        <v>110075</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="E79" s="8"/>
-      <c r="F79" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="7">
-        <v>110076</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7">
-        <v>110077</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-    </row>
-    <row r="82" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7">
-        <v>110078</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="E82" s="8"/>
-      <c r="F82" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7">
-        <v>110079</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="E83" s="8"/>
-      <c r="F83" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7">
-        <v>110080</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-    </row>
-    <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7">
-        <v>110081</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E85" s="8"/>
-      <c r="F85" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7">
-        <v>110082</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-    </row>
-    <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="7">
-        <v>110083</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="E87" s="8"/>
-      <c r="F87" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="7">
-        <v>110084</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-    </row>
-    <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="7">
-        <v>110085</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-    </row>
-    <row r="90" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7">
-        <v>110086</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-    </row>
-    <row r="91" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="7">
-        <v>110087</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-    </row>
-    <row r="92" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="7">
-        <v>110088</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="E92" s="8"/>
-      <c r="F92" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="7">
-        <v>110089</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="7">
-        <v>110090</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-    </row>
-    <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="7">
-        <v>110091</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-    </row>
-    <row r="96" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="7">
-        <v>110092</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E96" s="8"/>
-      <c r="F96" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="7">
-        <v>110093</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="E97" s="8"/>
-      <c r="F97" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="7">
-        <v>110094</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="E98" s="8"/>
-      <c r="F98" s="7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
-        <v>110095</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-    </row>
-    <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="7">
-        <v>110096</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-    </row>
-    <row r="101" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="7">
-        <v>110097</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="E101" s="8"/>
-      <c r="F101" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="7">
-        <v>110098</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-    </row>
-    <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="7">
-        <v>110099</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-    </row>
-    <row r="104" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="7">
-        <v>110100</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="E104" s="8"/>
-      <c r="F104" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="7">
-        <v>110101</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-    </row>
-    <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="7">
-        <v>190001</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-    </row>
-    <row r="107" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="7">
-        <v>190002</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E107" s="8"/>
-      <c r="F107" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="7">
-        <v>190101</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-    </row>
-    <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="7">
-        <v>190102</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F141">
-    <sortCondition ref="A2:A141"/>
-  </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Assets/DataTable/DataTable.xlsx
+++ b/Assets/DataTable/DataTable.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcbj1\Desktop\데이터테이블\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4939C27-5D71-4E43-9423-3AFA82FC0C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C89DADF-1CE2-4049-B802-725A44940926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="3" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="2" xr2:uid="{00093708-AE6C-4A54-80A8-1C4208CE031C}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemDataTable" sheetId="1" r:id="rId1"/>
     <sheet name="ItemDataTable_Meta" sheetId="7" r:id="rId2"/>
-    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId3"/>
-    <sheet name="ProductDataTable" sheetId="3" r:id="rId4"/>
-    <sheet name="Calculator" sheetId="14" r:id="rId5"/>
-    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId6"/>
-    <sheet name="EventDataTable" sheetId="4" r:id="rId7"/>
-    <sheet name="ObjectDataTable" sheetId="5" r:id="rId8"/>
-    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId9"/>
-    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId10"/>
+    <sheet name="LocalizationTable" sheetId="15" r:id="rId3"/>
+    <sheet name="KeycodeDataTable" sheetId="13" r:id="rId4"/>
+    <sheet name="ProductDataTable" sheetId="3" r:id="rId5"/>
+    <sheet name="Calculator" sheetId="14" r:id="rId6"/>
+    <sheet name="ProductDataTable_Meta" sheetId="8" r:id="rId7"/>
+    <sheet name="EventDataTable" sheetId="4" r:id="rId8"/>
+    <sheet name="ObjectDataTable" sheetId="5" r:id="rId9"/>
+    <sheet name="ObjectDataTable_Meta" sheetId="12" r:id="rId10"/>
+    <sheet name="BIC_ScenarioDataTable" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="398">
   <si>
     <t>ItemID</t>
   </si>
@@ -814,15 +815,9 @@
     <t>플레이어님의 쾌적하고 안전한 아가레아 생활을 위해 각종 수칙들을 설명드리도록 하겠습니다.</t>
   </si>
   <si>
-    <t>튜토리얼을 진행하시겠다면 Go, 바로 게임으로 들어가시겠다면 Skip을 눌러주세요.</t>
-  </si>
-  <si>
     <t>Tutorial_BIC_Manual</t>
   </si>
   <si>
-    <t>그러면 우선 슈트 조작 방법을 설명드리겠습니다.</t>
-  </si>
-  <si>
     <t>화면에 반짝이는 타일에 우클릭을 해보세요.</t>
   </si>
   <si>
@@ -967,15 +962,6 @@
     <t>수확할 때 마다 한 칸 씩 반짝이는 효과</t>
   </si>
   <si>
-    <t>수확한 아이템들은 모두 가운데에 있는 슬롯에 저장됩니다. 메인 인벤토리라고 부르죠.</t>
-  </si>
-  <si>
-    <t>처음 밭을 만들 때는 수분이 가득했지만, 한 번 수확을 마치면 밭이 마르게 됩니다.</t>
-  </si>
-  <si>
-    <t>부족한 수분은 방금 얻은 물병의 물을 사용해서 채울 수 있습니다. 이번엔 물병을 밭에 사용해보세요.</t>
-  </si>
-  <si>
     <t>마른 밭에는 작물을 심을 수 없기 때문에 심기 전에 물병으로 밭을 충분히 적셔줘야 합니다.</t>
   </si>
   <si>
@@ -1004,9 +990,6 @@
   </si>
   <si>
     <t>적재 모드에서는 창고와의 상호작용이 모두 우주선에서 이루어진다 생각하시면 되겠습니다.</t>
-  </si>
-  <si>
-    <t>그러면 감자를 더블 클릭하거나 우주선 슬롯에 드래그해서 적재를 해봅시다.</t>
   </si>
   <si>
     <t>창고에 있는 감자에 반짝이는 효과</t>
@@ -1340,6 +1323,874 @@
   <si>
     <t>아이템 ID 값을 입력하여 계산
 ID값은 2로 끝나는 작물 아이템이어야 한다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그러면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>감자를 우주선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬롯에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>드래그해서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적재를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해봅시다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>루크</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수확을 한 아이템은 모두</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가운데에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는 메인 인벤토리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>슬롯에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저장됩니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그리고 수확을 한 시점을 기준으로 유통기한이 생기게 됩니다. 유통기한 안에 판매를 하지 않으면 썩어서 없어지게 되니 조심하세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밭에는 처음</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>만들</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수분이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가득했지만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수확을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마치면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밭이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마르게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>됩니다.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밭이 마른 경우에는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>얻은</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물병의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용해 적셔줘야 합니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>밭에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사용해보세요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">튜토리얼 도중에 그만 건너뛰고 싶으시다면 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>ESC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버튼을 꾹 눌러보세요.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그러면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>우선</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">간단한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조작</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방법부터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명드리겠습니다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korean</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥수수 씨앗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>옥수수</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>씨 감자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근 씨앗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>당근</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>양파</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>양파 씨앗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸기 씨앗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>블루베리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>블구베리 씨앗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>빈 병</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>우유</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>물</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10만 골드</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정착 지원 패키지</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>닭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>소</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>베터리 LV1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 인벤토리 LV1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 인벤토리 LV2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브 인벤토리 LV1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>서브 인벤토리 LV2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>속도 LV1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>속도 LV2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>효율 LV1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>효율 LV2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>밭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>축사</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1347,7 +2198,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1525,6 +2376,40 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="39">
@@ -2003,7 +2888,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2042,6 +2927,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2094,7 +2988,7 @@
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="23">
     <dxf>
       <fill>
         <patternFill>
@@ -2127,6 +3021,69 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2523,7 +3480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6335F4D-6333-4BEC-B869-C3B1C6B3F47D}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
@@ -2916,10 +3873,10 @@
         <v>5011</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D17" s="2">
         <v>0</v>
@@ -2939,10 +3896,10 @@
         <v>5021</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D18" s="2">
         <v>0</v>
@@ -3238,7 +4195,7 @@
         <v>9001</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>52</v>
@@ -3279,7 +4236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>9021</v>
       </c>
@@ -3300,12 +4257,2542 @@
       </c>
       <c r="G33" s="2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L38" s="2" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G33">
     <sortCondition ref="A2:A33"/>
   </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="expression" dxfId="22" priority="1">
+      <formula>AND($A1 &gt;= 6000, $A1 &lt; 7000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="2">
+      <formula>AND($A1 &gt;= 7000, $A1 &lt; 8000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>AND($A1 &gt;= 5000, $A1 &lt; 6000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="4">
+      <formula>AND($A1 &gt;= 9000, $A1 &lt; 10000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="5">
+      <formula>AND($A1 &gt;=8000, $A1 &lt; 9000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="6">
+      <formula>AND($A1 &gt;= 4000, $A1 &lt; 5000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="7">
+      <formula>AND($A1 &gt;= 3000, $A1 &lt; 4000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="8">
+      <formula>AND($A1 &gt;= 2000, $A1 &lt; 3000)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="9">
+      <formula>AND($A1 &gt;= 1000, $A1 &lt; 2000)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A11">TRANSPOSE(ObjectDataTable!A1:J1)</f>
+        <v>ObjectID</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>ObjectName</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>ObjectType</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>Price</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <v>MainInv</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <v>SubInv</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <v>Speed</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <v>WorkDuration</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <v>ProductionAmount</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <v>UseToDemo</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
+  <dimension ref="A1:F110"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="25.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>100001</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>100002</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>100003</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>110001</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>365</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>110002</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>110003</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>110004</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>110005</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>110006</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="7">
+        <v>110007</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="7">
+        <v>110008</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
+        <v>110009</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="7">
+        <v>110010</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>110011</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>110012</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="7">
+        <v>110013</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="7">
+        <v>110014</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>110015</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>110016</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="7">
+        <v>110017</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7">
+        <v>110018</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7">
+        <v>110019</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7">
+        <v>110020</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="7">
+        <v>110021</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7">
+        <v>110022</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7">
+        <v>110023</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>110024</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>110025</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7">
+        <v>110026</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="7">
+        <v>110027</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7">
+        <v>110028</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E32" s="8"/>
+      <c r="F32" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="7">
+        <v>110029</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>110030</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>110031</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" s="8"/>
+      <c r="F35" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>110032</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="8"/>
+      <c r="F36" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
+        <v>110033</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>360</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="7">
+        <v>110034</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>361</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="8"/>
+    </row>
+    <row r="39" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="7">
+        <v>110035</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+    </row>
+    <row r="40" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="7">
+        <v>110036</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>363</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+    </row>
+    <row r="41" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="7">
+        <v>110037</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E41" s="8"/>
+      <c r="F41" s="8"/>
+    </row>
+    <row r="42" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="7">
+        <v>110038</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="7">
+        <v>110039</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="8"/>
+      <c r="F43" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7">
+        <v>110040</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+    </row>
+    <row r="45" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="7">
+        <v>110041</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E45" s="8"/>
+      <c r="F45" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="7">
+        <v>110042</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+    </row>
+    <row r="47" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="7">
+        <v>110043</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="E47" s="8"/>
+      <c r="F47" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="7">
+        <v>110044</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E48" s="8"/>
+      <c r="F48" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
+        <v>110045</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
+        <v>110046</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+    </row>
+    <row r="51" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="7">
+        <v>110047</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E51" s="8"/>
+      <c r="F51" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7">
+        <v>110048</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+    </row>
+    <row r="53" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="7">
+        <v>110049</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E53" s="8"/>
+      <c r="F53" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="7">
+        <v>110050</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E54" s="8"/>
+      <c r="F54" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="7">
+        <v>110051</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+    </row>
+    <row r="56" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="7">
+        <v>110052</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E56" s="8"/>
+      <c r="F56" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="7">
+        <v>110053</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+    </row>
+    <row r="58" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>110054</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+    </row>
+    <row r="59" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="7">
+        <v>110055</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+    </row>
+    <row r="60" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>110056</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
+        <v>110057</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E61" s="8"/>
+      <c r="F61" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
+        <v>110058</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+    </row>
+    <row r="63" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>110059</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+    </row>
+    <row r="64" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
+        <v>110060</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+    </row>
+    <row r="65" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>110061</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
+        <v>110062</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+    </row>
+    <row r="67" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>110063</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+    </row>
+    <row r="68" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
+        <v>110064</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E68" s="8"/>
+      <c r="F68" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>110065</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>110066</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E70" s="8"/>
+      <c r="F70" s="7" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="7">
+        <v>110067</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E71" s="8"/>
+      <c r="F71" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>110068</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E72" s="8"/>
+      <c r="F72" s="7" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="7">
+        <v>110069</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E73" s="8"/>
+      <c r="F73" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
+        <v>110070</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+    </row>
+    <row r="75" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="7">
+        <v>110071</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E75" s="8"/>
+      <c r="F75" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
+        <v>110072</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+    </row>
+    <row r="77" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
+        <v>110073</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+    </row>
+    <row r="78" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="7">
+        <v>110074</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+    </row>
+    <row r="79" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
+        <v>110075</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+    </row>
+    <row r="80" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>110076</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" s="8"/>
+      <c r="F80" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7">
+        <v>110077</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+    </row>
+    <row r="82" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="7">
+        <v>110078</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+    </row>
+    <row r="83" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>110079</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E83" s="8"/>
+      <c r="F83" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>110080</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E84" s="8"/>
+      <c r="F84" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>110081</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+    </row>
+    <row r="86" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7">
+        <v>110082</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="E86" s="8"/>
+      <c r="F86" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="7">
+        <v>110083</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+    </row>
+    <row r="88" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="7">
+        <v>110084</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="E88" s="8"/>
+      <c r="F88" s="9" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="7">
+        <v>110085</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+    </row>
+    <row r="90" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="7">
+        <v>110086</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+    </row>
+    <row r="91" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="7">
+        <v>110087</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+    </row>
+    <row r="92" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="7">
+        <v>110088</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+    </row>
+    <row r="93" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="7">
+        <v>110089</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E93" s="8"/>
+      <c r="F93" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="7">
+        <v>110090</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E94" s="8"/>
+      <c r="F94" s="7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="7">
+        <v>110091</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+    </row>
+    <row r="96" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="7">
+        <v>110092</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+    </row>
+    <row r="97" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="7">
+        <v>110093</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E97" s="8"/>
+      <c r="F97" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="7">
+        <v>110094</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E98" s="8"/>
+      <c r="F98" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="7">
+        <v>110095</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E99" s="8"/>
+      <c r="F99" s="7" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="7">
+        <v>110096</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+    </row>
+    <row r="101" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="7">
+        <v>110097</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+    </row>
+    <row r="102" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="7">
+        <v>110098</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E102" s="8"/>
+      <c r="F102" s="7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="7">
+        <v>110099</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+    </row>
+    <row r="104" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="7">
+        <v>110100</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E104" s="8"/>
+      <c r="F104" s="8"/>
+    </row>
+    <row r="105" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="7">
+        <v>110101</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E105" s="8"/>
+      <c r="F105" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="7">
+        <v>110102</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E106" s="8"/>
+      <c r="F106" s="8"/>
+    </row>
+    <row r="107" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="7">
+        <v>190001</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E107" s="8"/>
+      <c r="F107" s="8"/>
+    </row>
+    <row r="108" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="7">
+        <v>190002</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E108" s="8"/>
+      <c r="F108" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="7">
+        <v>190101</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E109" s="8"/>
+      <c r="F109" s="8"/>
+    </row>
+    <row r="110" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="7">
+        <v>190102</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E110" s="8"/>
+      <c r="F110" s="8"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F142">
+    <sortCondition ref="A2:A142"/>
+  </sortState>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="str" cm="1">
+        <f t="array" ref="A2:A7">TRANSPOSE(ItemDataTable!A1:F1)</f>
+        <v>ItemID</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="str">
+        <v>ItemName</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="str">
+        <v>ItemType</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="str">
+        <v>BasicPrice</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="str">
+        <v>Stack</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="str">
+        <v>StoragePeriod</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC52DA5-BF28-40FD-BA0C-E037F8F1DE98}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1011</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1012</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>1021</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>1022</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>2011</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>2012</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>3011</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>3012</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>3021</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>3022</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>4011</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>4012</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>5011</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C17" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>5021</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C18" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>6021</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>6031</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>6032</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>7011</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>8011</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>8012</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>8021</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>8022</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>8031</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>8032</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>8041</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>8042</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>9001</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C31" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>9011</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>9021</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="expression" dxfId="13" priority="1">
@@ -3337,1974 +6824,10 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2520165D-F660-4A4C-B4E3-D89CE2499B38}">
-  <dimension ref="A1:F109"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="25.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="122.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="74.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>100001</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>100002</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>100003</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>110001</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>110002</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>110003</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>110004</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>110005</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>110006</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>110007</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>110008</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>110009</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>110010</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>110011</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>110012</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>110013</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>110014</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>110015</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>110016</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>110017</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>110018</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>110019</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>110020</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>110021</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>110022</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
-        <v>110023</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>110024</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
-        <v>110025</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
-        <v>110026</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
-        <v>110027</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
-        <v>110028</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>110029</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
-        <v>110030</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E34" s="8"/>
-      <c r="F34" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>110031</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>110032</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>110033</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>110034</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
-        <v>110035</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
-        <v>110036</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
-        <v>110037</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
-        <v>110038</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
-        <v>110039</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
-        <v>110040</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
-        <v>110041</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
-        <v>110042</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
-        <v>110043</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
-        <v>110044</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E48" s="8"/>
-      <c r="F48" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
-        <v>110045</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-    </row>
-    <row r="50" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
-        <v>110046</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
-        <v>110047</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-    </row>
-    <row r="52" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
-        <v>110048</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E52" s="8"/>
-      <c r="F52" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
-        <v>110049</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="E53" s="8"/>
-      <c r="F53" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
-        <v>110050</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-    </row>
-    <row r="55" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
-        <v>110051</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E55" s="8"/>
-      <c r="F55" s="7" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
-        <v>110052</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-    </row>
-    <row r="57" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
-        <v>110053</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-    </row>
-    <row r="58" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
-        <v>110054</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-    </row>
-    <row r="59" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
-        <v>110055</v>
-      </c>
-      <c r="B59" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-    </row>
-    <row r="60" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
-        <v>110056</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
-        <v>110057</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-    </row>
-    <row r="62" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
-        <v>110058</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-    </row>
-    <row r="63" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
-        <v>110059</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-    </row>
-    <row r="64" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
-        <v>110060</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
-        <v>110061</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="7">
-        <v>110062</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-    </row>
-    <row r="67" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
-        <v>110063</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="E67" s="8"/>
-      <c r="F67" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="7">
-        <v>110064</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
-        <v>110065</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="7">
-        <v>110066</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="7">
-        <v>110067</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="E71" s="8"/>
-      <c r="F71" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7">
-        <v>110068</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="7">
-        <v>110069</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-    </row>
-    <row r="74" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7">
-        <v>110070</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E74" s="8"/>
-      <c r="F74" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="7">
-        <v>110071</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-    </row>
-    <row r="76" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="7">
-        <v>110072</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-    </row>
-    <row r="77" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="7">
-        <v>110073</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-    </row>
-    <row r="78" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="7">
-        <v>110074</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-    </row>
-    <row r="79" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
-        <v>110075</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="E79" s="8"/>
-      <c r="F79" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="7">
-        <v>110076</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
-    </row>
-    <row r="81" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7">
-        <v>110077</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
-    </row>
-    <row r="82" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7">
-        <v>110078</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="E82" s="8"/>
-      <c r="F82" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7">
-        <v>110079</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="E83" s="8"/>
-      <c r="F83" s="7" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7">
-        <v>110080</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
-    </row>
-    <row r="85" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7">
-        <v>110081</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E85" s="8"/>
-      <c r="F85" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7">
-        <v>110082</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="E86" s="8"/>
-      <c r="F86" s="8"/>
-    </row>
-    <row r="87" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="7">
-        <v>110083</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="E87" s="8"/>
-      <c r="F87" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="7">
-        <v>110084</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="E88" s="8"/>
-      <c r="F88" s="8"/>
-    </row>
-    <row r="89" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="7">
-        <v>110085</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-    </row>
-    <row r="90" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7">
-        <v>110086</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-    </row>
-    <row r="91" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="7">
-        <v>110087</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-    </row>
-    <row r="92" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="7">
-        <v>110088</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="E92" s="8"/>
-      <c r="F92" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="7">
-        <v>110089</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E93" s="8"/>
-      <c r="F93" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="7">
-        <v>110090</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-    </row>
-    <row r="95" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="7">
-        <v>110091</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-    </row>
-    <row r="96" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="7">
-        <v>110092</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E96" s="8"/>
-      <c r="F96" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="7">
-        <v>110093</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="E97" s="8"/>
-      <c r="F97" s="7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="7">
-        <v>110094</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="E98" s="8"/>
-      <c r="F98" s="7" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
-        <v>110095</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-    </row>
-    <row r="100" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="7">
-        <v>110096</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-    </row>
-    <row r="101" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="7">
-        <v>110097</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="E101" s="8"/>
-      <c r="F101" s="7" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="7">
-        <v>110098</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-    </row>
-    <row r="103" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="7">
-        <v>110099</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="E103" s="8"/>
-      <c r="F103" s="8"/>
-    </row>
-    <row r="104" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="7">
-        <v>110100</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="E104" s="8"/>
-      <c r="F104" s="7" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="7">
-        <v>110101</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-    </row>
-    <row r="106" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="7">
-        <v>190001</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="E106" s="8"/>
-      <c r="F106" s="8"/>
-    </row>
-    <row r="107" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="7">
-        <v>190002</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E107" s="8"/>
-      <c r="F107" s="7" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="7">
-        <v>190101</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
-    </row>
-    <row r="109" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="7">
-        <v>190102</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E109" s="8"/>
-      <c r="F109" s="8"/>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F141">
-    <sortCondition ref="A2:A141"/>
-  </sortState>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{448FCFD8-7062-4DFA-B86D-C27384DBCAB4}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="str" cm="1">
-        <f t="array" ref="A2:A7">TRANSPOSE(ItemDataTable!A1:F1)</f>
-        <v>ItemID</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="str">
-        <v>ItemName</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="str">
-        <v>ItemType</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="str">
-        <v>BasicPrice</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="str">
-        <v>Stack</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="str">
-        <v>StoragePeriod</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553D902D-6443-438F-90C7-179D093475FD}">
   <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5638,7 +7161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B20862AF-9F9A-48F1-AC3A-75C77964B415}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5920,7 +7443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67515829-0AFB-4F47-8C6E-31EBDF1B0551}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5933,41 +7456,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="A1" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -6020,7 +7543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1832395-F88D-430F-A64D-C09D9FD6DD70}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6147,7 +7670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3180EA1-F814-4A73-A11F-F66CD4A7D6E3}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6581,7 +8104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192613AC-7E74-42D9-8201-7830AAD06556}">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -6768,141 +8291,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F02C12FE-3D1B-4A6F-9A93-1E89BB0AD02C}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:A11">TRANSPOSE(ObjectDataTable!A1:J1)</f>
-        <v>ObjectID</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <v>ObjectName</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <v>ObjectType</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <v>Price</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <v>MainInv</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <v>SubInv</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <v>Speed</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <v>WorkDuration</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <v>ProductionAmount</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <v>UseToDemo</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>